--- a/hall/resources/sample/EmployeeLevel.xlsx
+++ b/hall/resources/sample/EmployeeLevel.xlsx
@@ -77,7 +77,7 @@
     <t>升级消耗</t>
   </si>
   <si>
-    <t>技能值</t>
+    <t>属性值</t>
   </si>
   <si>
     <t>int</t>

--- a/hall/resources/sample/EmployeeLevel.xlsx
+++ b/hall/resources/sample/EmployeeLevel.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="213">
   <si>
     <t>ID</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>Map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
     <t>Map&lt;int{_}int&gt;{|}</t>
@@ -1931,24 +1934,24 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1970,10 +1973,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1988,10 +1991,10 @@
         <v>2</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2006,10 +2009,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2024,10 +2027,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2042,10 +2045,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2060,10 +2063,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2078,10 +2081,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2096,10 +2099,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2114,10 +2117,10 @@
         <v>9</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2132,10 +2135,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2150,10 +2153,10 @@
         <v>1</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2168,10 +2171,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2186,10 +2189,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2204,10 +2207,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2222,10 +2225,10 @@
         <v>5</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2240,10 +2243,10 @@
         <v>6</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2258,10 +2261,10 @@
         <v>7</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2276,10 +2279,10 @@
         <v>8</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2294,10 +2297,10 @@
         <v>9</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2312,10 +2315,10 @@
         <v>10</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2330,10 +2333,10 @@
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2348,10 +2351,10 @@
         <v>2</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2366,10 +2369,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2384,10 +2387,10 @@
         <v>4</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2402,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2420,10 +2423,10 @@
         <v>6</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2438,10 +2441,10 @@
         <v>7</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2456,10 +2459,10 @@
         <v>8</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2474,10 +2477,10 @@
         <v>9</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2492,10 +2495,10 @@
         <v>10</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2510,10 +2513,10 @@
         <v>1</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2528,10 +2531,10 @@
         <v>2</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2546,10 +2549,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2564,10 +2567,10 @@
         <v>4</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2582,10 +2585,10 @@
         <v>5</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2600,10 +2603,10 @@
         <v>6</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2618,10 +2621,10 @@
         <v>7</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2636,10 +2639,10 @@
         <v>8</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2654,10 +2657,10 @@
         <v>9</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2672,10 +2675,10 @@
         <v>10</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2690,10 +2693,10 @@
         <v>1</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2708,10 +2711,10 @@
         <v>2</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2726,10 +2729,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2744,10 +2747,10 @@
         <v>4</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2762,10 +2765,10 @@
         <v>5</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2780,10 +2783,10 @@
         <v>6</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2798,10 +2801,10 @@
         <v>7</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2816,10 +2819,10 @@
         <v>8</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2834,10 +2837,10 @@
         <v>9</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2852,10 +2855,10 @@
         <v>10</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2870,10 +2873,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2888,10 +2891,10 @@
         <v>2</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2906,10 +2909,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2924,10 +2927,10 @@
         <v>4</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2942,10 +2945,10 @@
         <v>5</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2960,10 +2963,10 @@
         <v>6</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2978,10 +2981,10 @@
         <v>7</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2996,10 +2999,10 @@
         <v>8</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3014,10 +3017,10 @@
         <v>9</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3032,10 +3035,10 @@
         <v>10</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3050,10 +3053,10 @@
         <v>1</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3068,10 +3071,10 @@
         <v>2</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3086,10 +3089,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3104,10 +3107,10 @@
         <v>4</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3122,10 +3125,10 @@
         <v>5</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3140,10 +3143,10 @@
         <v>6</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3158,10 +3161,10 @@
         <v>7</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3176,10 +3179,10 @@
         <v>8</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3194,10 +3197,10 @@
         <v>9</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3212,10 +3215,10 @@
         <v>10</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3230,10 +3233,10 @@
         <v>1</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3248,10 +3251,10 @@
         <v>2</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3266,10 +3269,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3284,10 +3287,10 @@
         <v>4</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -3302,10 +3305,10 @@
         <v>5</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3320,10 +3323,10 @@
         <v>6</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3338,10 +3341,10 @@
         <v>7</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3356,10 +3359,10 @@
         <v>8</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3374,10 +3377,10 @@
         <v>9</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -3392,10 +3395,10 @@
         <v>10</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -3410,10 +3413,10 @@
         <v>1</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3428,10 +3431,10 @@
         <v>2</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3446,10 +3449,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3464,10 +3467,10 @@
         <v>4</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3482,10 +3485,10 @@
         <v>5</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3500,10 +3503,10 @@
         <v>6</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3518,10 +3521,10 @@
         <v>7</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3536,10 +3539,10 @@
         <v>8</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3554,10 +3557,10 @@
         <v>9</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3572,10 +3575,10 @@
         <v>10</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -3590,10 +3593,10 @@
         <v>1</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3608,10 +3611,10 @@
         <v>2</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -3626,10 +3629,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -3644,10 +3647,10 @@
         <v>4</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3662,10 +3665,10 @@
         <v>5</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -3680,10 +3683,10 @@
         <v>6</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -3698,10 +3701,10 @@
         <v>7</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3716,10 +3719,10 @@
         <v>8</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -3734,10 +3737,10 @@
         <v>9</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3752,10 +3755,10 @@
         <v>10</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3770,10 +3773,10 @@
         <v>1</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -3788,10 +3791,10 @@
         <v>2</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3806,10 +3809,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3824,10 +3827,10 @@
         <v>4</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3842,10 +3845,10 @@
         <v>5</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3860,10 +3863,10 @@
         <v>6</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3878,10 +3881,10 @@
         <v>7</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3896,10 +3899,10 @@
         <v>8</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3914,10 +3917,10 @@
         <v>9</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3932,10 +3935,10 @@
         <v>10</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3950,10 +3953,10 @@
         <v>1</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3968,10 +3971,10 @@
         <v>2</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3986,10 +3989,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -4004,10 +4007,10 @@
         <v>4</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -4022,10 +4025,10 @@
         <v>5</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4040,10 +4043,10 @@
         <v>6</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -4058,10 +4061,10 @@
         <v>7</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4076,10 +4079,10 @@
         <v>8</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -4094,10 +4097,10 @@
         <v>9</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -4112,10 +4115,10 @@
         <v>10</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -4130,10 +4133,10 @@
         <v>1</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -4148,10 +4151,10 @@
         <v>2</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -4166,10 +4169,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -4184,10 +4187,10 @@
         <v>4</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -4202,10 +4205,10 @@
         <v>5</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -4220,10 +4223,10 @@
         <v>6</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -4238,10 +4241,10 @@
         <v>7</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -4256,10 +4259,10 @@
         <v>8</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -4274,10 +4277,10 @@
         <v>9</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -4292,10 +4295,10 @@
         <v>10</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -4310,10 +4313,10 @@
         <v>1</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -4328,10 +4331,10 @@
         <v>2</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -4346,10 +4349,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -4364,10 +4367,10 @@
         <v>4</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -4382,10 +4385,10 @@
         <v>5</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -4400,10 +4403,10 @@
         <v>6</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -4418,10 +4421,10 @@
         <v>7</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -4436,10 +4439,10 @@
         <v>8</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -4454,10 +4457,10 @@
         <v>9</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -4472,10 +4475,10 @@
         <v>10</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -4490,10 +4493,10 @@
         <v>1</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -4508,10 +4511,10 @@
         <v>2</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -4526,10 +4529,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -4544,10 +4547,10 @@
         <v>4</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -4562,10 +4565,10 @@
         <v>5</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -4580,10 +4583,10 @@
         <v>6</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -4598,10 +4601,10 @@
         <v>7</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -4616,10 +4619,10 @@
         <v>8</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -4634,10 +4637,10 @@
         <v>9</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -4652,10 +4655,10 @@
         <v>10</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/EmployeeLevel.xlsx
+++ b/hall/resources/sample/EmployeeLevel.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="294">
   <si>
     <t>ID</t>
   </si>
@@ -167,541 +167,784 @@
     <t>1024008_5000</t>
   </si>
   <si>
-    <t>5_2100</t>
-  </si>
-  <si>
     <t>1024008_5100</t>
   </si>
   <si>
-    <t>5_2200</t>
-  </si>
-  <si>
     <t>1024008_5200</t>
   </si>
   <si>
-    <t>5_2300</t>
-  </si>
-  <si>
     <t>1024008_5300</t>
   </si>
   <si>
-    <t>5_2400</t>
+    <t>3_1000</t>
   </si>
   <si>
     <t>1024008_5400</t>
   </si>
   <si>
-    <t>5_2500</t>
+    <t>3_1200</t>
   </si>
   <si>
     <t>1024008_5500</t>
   </si>
   <si>
-    <t>5_2600</t>
+    <t>3_1400</t>
   </si>
   <si>
     <t>1024008_5600</t>
   </si>
   <si>
-    <t>5_2700</t>
+    <t>3_1600</t>
   </si>
   <si>
     <t>1024008_5700</t>
   </si>
   <si>
-    <t>5_2800</t>
+    <t>3_1800</t>
   </si>
   <si>
     <t>1024008_5800</t>
   </si>
   <si>
-    <t>5_2900</t>
-  </si>
-  <si>
     <t>1024008_5900</t>
   </si>
   <si>
-    <t>5_3000</t>
+    <t>3_3000</t>
   </si>
   <si>
     <t>1024008_10000</t>
   </si>
   <si>
+    <t>1024008_10100</t>
+  </si>
+  <si>
+    <t>1024008_10200</t>
+  </si>
+  <si>
+    <t>3_1100</t>
+  </si>
+  <si>
+    <t>1024008_10300</t>
+  </si>
+  <si>
+    <t>1024008_10400</t>
+  </si>
+  <si>
+    <t>3_1700</t>
+  </si>
+  <si>
+    <t>1024008_10500</t>
+  </si>
+  <si>
+    <t>1024008_10600</t>
+  </si>
+  <si>
+    <t>3_2300</t>
+  </si>
+  <si>
+    <t>1024008_10700</t>
+  </si>
+  <si>
+    <t>3_2600</t>
+  </si>
+  <si>
+    <t>1024008_10800</t>
+  </si>
+  <si>
+    <t>3_2900</t>
+  </si>
+  <si>
+    <t>1024008_10900</t>
+  </si>
+  <si>
+    <t>3_4000</t>
+  </si>
+  <si>
+    <t>1024008_15000</t>
+  </si>
+  <si>
+    <t>1024008_15100</t>
+  </si>
+  <si>
+    <t>1024008_15200</t>
+  </si>
+  <si>
+    <t>1024008_15300</t>
+  </si>
+  <si>
+    <t>1024008_15400</t>
+  </si>
+  <si>
+    <t>3_2200</t>
+  </si>
+  <si>
+    <t>1024008_15500</t>
+  </si>
+  <si>
+    <t>1024008_15600</t>
+  </si>
+  <si>
+    <t>1024008_15700</t>
+  </si>
+  <si>
+    <t>3_3400</t>
+  </si>
+  <si>
+    <t>1024008_15800</t>
+  </si>
+  <si>
+    <t>3_3800</t>
+  </si>
+  <si>
+    <t>1024008_15900</t>
+  </si>
+  <si>
     <t>3_5000</t>
   </si>
   <si>
-    <t>1024008_10100</t>
-  </si>
-  <si>
-    <t>3_5100</t>
-  </si>
-  <si>
-    <t>1024008_10200</t>
-  </si>
-  <si>
-    <t>3_5200</t>
-  </si>
-  <si>
-    <t>1024008_10300</t>
-  </si>
-  <si>
-    <t>3_5300</t>
-  </si>
-  <si>
-    <t>1024008_10400</t>
-  </si>
-  <si>
-    <t>3_5400</t>
-  </si>
-  <si>
-    <t>1024008_10500</t>
-  </si>
-  <si>
-    <t>3_5500</t>
-  </si>
-  <si>
-    <t>1024008_10600</t>
-  </si>
-  <si>
-    <t>3_5600</t>
-  </si>
-  <si>
-    <t>1024008_10700</t>
-  </si>
-  <si>
-    <t>3_5700</t>
-  </si>
-  <si>
-    <t>1024008_10800</t>
-  </si>
-  <si>
-    <t>3_5800</t>
-  </si>
-  <si>
-    <t>1024008_10900</t>
-  </si>
-  <si>
-    <t>3_5900</t>
-  </si>
-  <si>
-    <t>1024008_15000</t>
+    <t>1024008_20000</t>
+  </si>
+  <si>
+    <t>1024008_20100</t>
+  </si>
+  <si>
+    <t>3_1500</t>
+  </si>
+  <si>
+    <t>1024008_20200</t>
+  </si>
+  <si>
+    <t>1024008_20300</t>
+  </si>
+  <si>
+    <t>3_2500</t>
+  </si>
+  <si>
+    <t>1024008_20400</t>
+  </si>
+  <si>
+    <t>1024008_20500</t>
+  </si>
+  <si>
+    <t>3_3500</t>
+  </si>
+  <si>
+    <t>1024008_20600</t>
+  </si>
+  <si>
+    <t>1024008_20700</t>
+  </si>
+  <si>
+    <t>3_4500</t>
+  </si>
+  <si>
+    <t>1024008_20800</t>
+  </si>
+  <si>
+    <t>1024008_20900</t>
   </si>
   <si>
     <t>3_8000</t>
   </si>
   <si>
-    <t>1024008_15100</t>
-  </si>
-  <si>
-    <t>3_8100</t>
-  </si>
-  <si>
-    <t>1024008_15200</t>
-  </si>
-  <si>
-    <t>3_8200</t>
-  </si>
-  <si>
-    <t>1024008_15300</t>
-  </si>
-  <si>
-    <t>3_8300</t>
-  </si>
-  <si>
-    <t>1024008_15400</t>
-  </si>
-  <si>
-    <t>3_8400</t>
-  </si>
-  <si>
-    <t>1024008_15500</t>
-  </si>
-  <si>
-    <t>3_8500</t>
-  </si>
-  <si>
-    <t>1024008_15600</t>
-  </si>
-  <si>
-    <t>3_8600</t>
-  </si>
-  <si>
-    <t>1024008_15700</t>
-  </si>
-  <si>
-    <t>3_8700</t>
-  </si>
-  <si>
-    <t>1024008_15800</t>
-  </si>
-  <si>
-    <t>3_8800</t>
-  </si>
-  <si>
-    <t>1024008_15900</t>
-  </si>
-  <si>
-    <t>3_8900</t>
-  </si>
-  <si>
-    <t>1024008_20000</t>
-  </si>
-  <si>
-    <t>3_10000</t>
-  </si>
-  <si>
-    <t>1024008_20100</t>
-  </si>
-  <si>
-    <t>3_10100</t>
-  </si>
-  <si>
-    <t>1024008_20200</t>
-  </si>
-  <si>
-    <t>3_10200</t>
-  </si>
-  <si>
-    <t>1024008_20300</t>
-  </si>
-  <si>
-    <t>3_10300</t>
-  </si>
-  <si>
-    <t>1024008_20400</t>
-  </si>
-  <si>
-    <t>3_10400</t>
-  </si>
-  <si>
-    <t>1024008_20500</t>
-  </si>
-  <si>
-    <t>3_10500</t>
-  </si>
-  <si>
-    <t>1024008_20600</t>
-  </si>
-  <si>
-    <t>3_10600</t>
-  </si>
-  <si>
-    <t>1024008_20700</t>
-  </si>
-  <si>
-    <t>3_10700</t>
-  </si>
-  <si>
-    <t>1024008_20800</t>
-  </si>
-  <si>
-    <t>3_10800</t>
-  </si>
-  <si>
-    <t>1024008_20900</t>
-  </si>
-  <si>
-    <t>3_10900</t>
-  </si>
-  <si>
     <t>1024009_1000</t>
   </si>
   <si>
+    <t>5_100</t>
+  </si>
+  <si>
     <t>1024009_1100</t>
   </si>
   <si>
+    <t>5_110</t>
+  </si>
+  <si>
     <t>1024009_1200</t>
   </si>
   <si>
+    <t>5_120</t>
+  </si>
+  <si>
     <t>1024009_1300</t>
   </si>
   <si>
+    <t>5_130</t>
+  </si>
+  <si>
     <t>1024009_1400</t>
   </si>
   <si>
+    <t>5_140</t>
+  </si>
+  <si>
     <t>1024009_1500</t>
   </si>
   <si>
+    <t>5_150</t>
+  </si>
+  <si>
     <t>1024009_1600</t>
   </si>
   <si>
+    <t>5_160</t>
+  </si>
+  <si>
     <t>1024009_1700</t>
   </si>
   <si>
+    <t>5_170</t>
+  </si>
+  <si>
     <t>1024009_1800</t>
   </si>
   <si>
+    <t>5_180</t>
+  </si>
+  <si>
     <t>1024009_1900</t>
   </si>
   <si>
+    <t>5_190</t>
+  </si>
+  <si>
     <t>1024009_5000</t>
   </si>
   <si>
+    <t>5_200</t>
+  </si>
+  <si>
     <t>1024009_5100</t>
   </si>
   <si>
+    <t>5_210</t>
+  </si>
+  <si>
     <t>1024009_5200</t>
   </si>
   <si>
+    <t>5_220</t>
+  </si>
+  <si>
     <t>1024009_5300</t>
   </si>
   <si>
+    <t>5_230</t>
+  </si>
+  <si>
     <t>1024009_5400</t>
   </si>
   <si>
+    <t>5_240</t>
+  </si>
+  <si>
     <t>1024009_5500</t>
   </si>
   <si>
+    <t>5_250</t>
+  </si>
+  <si>
     <t>1024009_5600</t>
   </si>
   <si>
+    <t>5_260</t>
+  </si>
+  <si>
     <t>1024009_5700</t>
   </si>
   <si>
+    <t>5_270</t>
+  </si>
+  <si>
     <t>1024009_5800</t>
   </si>
   <si>
+    <t>5_280</t>
+  </si>
+  <si>
     <t>1024009_5900</t>
   </si>
   <si>
+    <t>5_290</t>
+  </si>
+  <si>
     <t>1024009_10000</t>
   </si>
   <si>
+    <t>5_300</t>
+  </si>
+  <si>
     <t>1024009_10100</t>
   </si>
   <si>
+    <t>5_310</t>
+  </si>
+  <si>
     <t>1024009_10200</t>
   </si>
   <si>
+    <t>5_320</t>
+  </si>
+  <si>
     <t>1024009_10300</t>
   </si>
   <si>
+    <t>5_330</t>
+  </si>
+  <si>
     <t>1024009_10400</t>
   </si>
   <si>
+    <t>5_340</t>
+  </si>
+  <si>
     <t>1024009_10500</t>
   </si>
   <si>
+    <t>5_350</t>
+  </si>
+  <si>
     <t>1024009_10600</t>
   </si>
   <si>
+    <t>5_360</t>
+  </si>
+  <si>
     <t>1024009_10700</t>
   </si>
   <si>
+    <t>5_370</t>
+  </si>
+  <si>
     <t>1024009_10800</t>
   </si>
   <si>
+    <t>5_380</t>
+  </si>
+  <si>
     <t>1024009_10900</t>
   </si>
   <si>
+    <t>5_390</t>
+  </si>
+  <si>
     <t>1024009_15000</t>
   </si>
   <si>
+    <t>5_400</t>
+  </si>
+  <si>
     <t>1024009_15100</t>
   </si>
   <si>
+    <t>5_410</t>
+  </si>
+  <si>
     <t>1024009_15200</t>
   </si>
   <si>
+    <t>5_420</t>
+  </si>
+  <si>
     <t>1024009_15300</t>
   </si>
   <si>
+    <t>5_430</t>
+  </si>
+  <si>
     <t>1024009_15400</t>
   </si>
   <si>
+    <t>5_440</t>
+  </si>
+  <si>
     <t>1024009_15500</t>
   </si>
   <si>
+    <t>5_450</t>
+  </si>
+  <si>
     <t>1024009_15600</t>
   </si>
   <si>
+    <t>5_460</t>
+  </si>
+  <si>
     <t>1024009_15700</t>
   </si>
   <si>
+    <t>5_470</t>
+  </si>
+  <si>
     <t>1024009_15800</t>
   </si>
   <si>
+    <t>5_480</t>
+  </si>
+  <si>
     <t>1024009_15900</t>
   </si>
   <si>
+    <t>5_490</t>
+  </si>
+  <si>
     <t>1024009_20000</t>
   </si>
   <si>
+    <t>5_500</t>
+  </si>
+  <si>
     <t>1024009_20100</t>
   </si>
   <si>
+    <t>5_510</t>
+  </si>
+  <si>
     <t>1024009_20200</t>
   </si>
   <si>
+    <t>5_520</t>
+  </si>
+  <si>
     <t>1024009_20300</t>
   </si>
   <si>
+    <t>5_530</t>
+  </si>
+  <si>
     <t>1024009_20400</t>
   </si>
   <si>
+    <t>5_540</t>
+  </si>
+  <si>
     <t>1024009_20500</t>
   </si>
   <si>
+    <t>5_550</t>
+  </si>
+  <si>
     <t>1024009_20600</t>
   </si>
   <si>
+    <t>5_560</t>
+  </si>
+  <si>
     <t>1024009_20700</t>
   </si>
   <si>
+    <t>5_570</t>
+  </si>
+  <si>
     <t>1024009_20800</t>
   </si>
   <si>
+    <t>5_580</t>
+  </si>
+  <si>
     <t>1024009_20900</t>
   </si>
   <si>
+    <t>5_590</t>
+  </si>
+  <si>
     <t>1024010_1000</t>
   </si>
   <si>
+    <t>4_100</t>
+  </si>
+  <si>
     <t>1024010_1100</t>
   </si>
   <si>
+    <t>4_110</t>
+  </si>
+  <si>
     <t>1024010_1200</t>
   </si>
   <si>
+    <t>4_120</t>
+  </si>
+  <si>
     <t>1024010_1300</t>
   </si>
   <si>
+    <t>4_130</t>
+  </si>
+  <si>
     <t>1024010_1400</t>
   </si>
   <si>
+    <t>4_140</t>
+  </si>
+  <si>
     <t>1024010_1500</t>
   </si>
   <si>
+    <t>4_150</t>
+  </si>
+  <si>
     <t>1024010_1600</t>
   </si>
   <si>
+    <t>4_160</t>
+  </si>
+  <si>
     <t>1024010_1700</t>
   </si>
   <si>
+    <t>4_170</t>
+  </si>
+  <si>
     <t>1024010_1800</t>
   </si>
   <si>
+    <t>4_180</t>
+  </si>
+  <si>
     <t>1024010_1900</t>
   </si>
   <si>
+    <t>4_190</t>
+  </si>
+  <si>
     <t>1024010_5000</t>
   </si>
   <si>
+    <t>4_200</t>
+  </si>
+  <si>
     <t>1024010_5100</t>
   </si>
   <si>
+    <t>4_210</t>
+  </si>
+  <si>
     <t>1024010_5200</t>
   </si>
   <si>
+    <t>4_220</t>
+  </si>
+  <si>
     <t>1024010_5300</t>
   </si>
   <si>
+    <t>4_230</t>
+  </si>
+  <si>
     <t>1024010_5400</t>
   </si>
   <si>
+    <t>4_240</t>
+  </si>
+  <si>
     <t>1024010_5500</t>
   </si>
   <si>
+    <t>4_250</t>
+  </si>
+  <si>
     <t>1024010_5600</t>
   </si>
   <si>
+    <t>4_260</t>
+  </si>
+  <si>
     <t>1024010_5700</t>
   </si>
   <si>
+    <t>4_270</t>
+  </si>
+  <si>
     <t>1024010_5800</t>
   </si>
   <si>
+    <t>4_280</t>
+  </si>
+  <si>
     <t>1024010_5900</t>
   </si>
   <si>
+    <t>4_290</t>
+  </si>
+  <si>
     <t>1024010_10000</t>
   </si>
   <si>
+    <t>4_300</t>
+  </si>
+  <si>
     <t>1024010_10100</t>
   </si>
   <si>
+    <t>4_310</t>
+  </si>
+  <si>
     <t>1024010_10200</t>
   </si>
   <si>
+    <t>4_320</t>
+  </si>
+  <si>
     <t>1024010_10300</t>
   </si>
   <si>
+    <t>4_330</t>
+  </si>
+  <si>
     <t>1024010_10400</t>
   </si>
   <si>
+    <t>4_340</t>
+  </si>
+  <si>
     <t>1024010_10500</t>
   </si>
   <si>
+    <t>4_350</t>
+  </si>
+  <si>
     <t>1024010_10600</t>
   </si>
   <si>
+    <t>4_360</t>
+  </si>
+  <si>
     <t>1024010_10700</t>
   </si>
   <si>
+    <t>4_370</t>
+  </si>
+  <si>
     <t>1024010_10800</t>
   </si>
   <si>
+    <t>4_380</t>
+  </si>
+  <si>
     <t>1024010_10900</t>
   </si>
   <si>
+    <t>4_390</t>
+  </si>
+  <si>
     <t>1024010_15000</t>
   </si>
   <si>
+    <t>4_400</t>
+  </si>
+  <si>
     <t>1024010_15100</t>
   </si>
   <si>
+    <t>4_410</t>
+  </si>
+  <si>
     <t>1024010_15200</t>
   </si>
   <si>
+    <t>4_420</t>
+  </si>
+  <si>
     <t>1024010_15300</t>
   </si>
   <si>
+    <t>4_430</t>
+  </si>
+  <si>
     <t>1024010_15400</t>
   </si>
   <si>
+    <t>4_440</t>
+  </si>
+  <si>
     <t>1024010_15500</t>
   </si>
   <si>
+    <t>4_450</t>
+  </si>
+  <si>
     <t>1024010_15600</t>
   </si>
   <si>
+    <t>4_460</t>
+  </si>
+  <si>
     <t>1024010_15700</t>
   </si>
   <si>
+    <t>4_470</t>
+  </si>
+  <si>
     <t>1024010_15800</t>
   </si>
   <si>
+    <t>4_480</t>
+  </si>
+  <si>
     <t>1024010_15900</t>
   </si>
   <si>
+    <t>4_490</t>
+  </si>
+  <si>
     <t>1024010_20000</t>
   </si>
   <si>
+    <t>4_500</t>
+  </si>
+  <si>
     <t>1024010_20100</t>
   </si>
   <si>
+    <t>4_510</t>
+  </si>
+  <si>
     <t>1024010_20200</t>
   </si>
   <si>
+    <t>4_520</t>
+  </si>
+  <si>
     <t>1024010_20300</t>
   </si>
   <si>
+    <t>4_530</t>
+  </si>
+  <si>
     <t>1024010_20400</t>
   </si>
   <si>
+    <t>4_540</t>
+  </si>
+  <si>
     <t>1024010_20500</t>
   </si>
   <si>
+    <t>4_550</t>
+  </si>
+  <si>
     <t>1024010_20600</t>
   </si>
   <si>
+    <t>4_560</t>
+  </si>
+  <si>
     <t>1024010_20700</t>
   </si>
   <si>
+    <t>4_570</t>
+  </si>
+  <si>
     <t>1024010_20800</t>
   </si>
   <si>
+    <t>4_580</t>
+  </si>
+  <si>
     <t>1024010_20900</t>
+  </si>
+  <si>
+    <t>4_590</t>
   </si>
 </sst>
 </file>
@@ -878,7 +1121,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -888,6 +1131,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1225,7 +1474,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1249,16 +1498,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1267,89 +1516,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1367,6 +1616,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1893,7 +2145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -2156,7 +2408,7 @@
         <v>33</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2171,10 +2423,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2189,10 +2441,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2207,10 +2459,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2225,10 +2477,10 @@
         <v>5</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2243,10 +2495,10 @@
         <v>6</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2261,10 +2513,10 @@
         <v>7</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2279,10 +2531,10 @@
         <v>8</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2297,10 +2549,10 @@
         <v>9</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2315,10 +2567,10 @@
         <v>10</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2333,10 +2585,10 @@
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2351,10 +2603,10 @@
         <v>2</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2369,10 +2621,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2387,10 +2639,10 @@
         <v>4</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2405,10 +2657,10 @@
         <v>5</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2423,10 +2675,10 @@
         <v>6</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2441,10 +2693,10 @@
         <v>7</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2459,10 +2711,10 @@
         <v>8</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2477,10 +2729,10 @@
         <v>9</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2495,10 +2747,10 @@
         <v>10</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2513,10 +2765,10 @@
         <v>1</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2531,10 +2783,10 @@
         <v>2</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2549,10 +2801,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2567,10 +2819,10 @@
         <v>4</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2585,10 +2837,10 @@
         <v>5</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2603,10 +2855,10 @@
         <v>6</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2621,10 +2873,10 @@
         <v>7</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2639,10 +2891,10 @@
         <v>8</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2657,10 +2909,10 @@
         <v>9</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2675,10 +2927,10 @@
         <v>10</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2693,10 +2945,10 @@
         <v>1</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2711,10 +2963,10 @@
         <v>2</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>96</v>
+        <v>80</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2729,10 +2981,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>98</v>
+        <v>82</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2747,10 +2999,10 @@
         <v>4</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>100</v>
+        <v>83</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2765,10 +3017,10 @@
         <v>5</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>102</v>
+        <v>85</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2783,10 +3035,10 @@
         <v>6</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>104</v>
+        <v>86</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2801,10 +3053,10 @@
         <v>7</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>106</v>
+        <v>88</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2819,10 +3071,10 @@
         <v>8</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>108</v>
+        <v>89</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2837,10 +3089,10 @@
         <v>9</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>110</v>
+        <v>91</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2855,10 +3107,10 @@
         <v>10</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2873,10 +3125,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2891,10 +3143,10 @@
         <v>2</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2909,10 +3161,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2927,10 +3179,10 @@
         <v>4</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2945,10 +3197,10 @@
         <v>5</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>22</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2963,10 +3215,10 @@
         <v>6</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2981,10 +3233,10 @@
         <v>7</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2999,10 +3251,10 @@
         <v>8</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3017,10 +3269,10 @@
         <v>9</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3035,10 +3287,10 @@
         <v>10</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3053,10 +3305,10 @@
         <v>1</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>34</v>
+        <v>114</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3071,10 +3323,10 @@
         <v>2</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>36</v>
+        <v>116</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3089,10 +3341,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>38</v>
+        <v>118</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3107,10 +3359,10 @@
         <v>4</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>40</v>
+        <v>120</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3125,10 +3377,10 @@
         <v>5</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>42</v>
+        <v>122</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3143,10 +3395,10 @@
         <v>6</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>44</v>
+        <v>124</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3161,10 +3413,10 @@
         <v>7</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>46</v>
+        <v>126</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3179,10 +3431,10 @@
         <v>8</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>48</v>
+        <v>128</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3197,10 +3449,10 @@
         <v>9</v>
       </c>
       <c r="D73" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E73" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3217,8 +3469,8 @@
       <c r="D74" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>52</v>
+      <c r="E74" s="4" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3233,10 +3485,10 @@
         <v>1</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3251,10 +3503,10 @@
         <v>2</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3269,10 +3521,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3287,10 +3539,10 @@
         <v>4</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -3305,10 +3557,10 @@
         <v>5</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3323,10 +3575,10 @@
         <v>6</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3341,10 +3593,10 @@
         <v>7</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3359,10 +3611,10 @@
         <v>8</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>68</v>
+        <v>149</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3377,10 +3629,10 @@
         <v>9</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -3395,10 +3647,10 @@
         <v>10</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>72</v>
+        <v>153</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -3413,10 +3665,10 @@
         <v>1</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>74</v>
+        <v>154</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3431,10 +3683,10 @@
         <v>2</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>76</v>
+        <v>156</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3449,10 +3701,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>78</v>
+        <v>158</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3467,10 +3719,10 @@
         <v>4</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>80</v>
+        <v>160</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3485,10 +3737,10 @@
         <v>5</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>82</v>
+        <v>162</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3503,10 +3755,10 @@
         <v>6</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>84</v>
+        <v>164</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3521,10 +3773,10 @@
         <v>7</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>86</v>
+        <v>166</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3539,10 +3791,10 @@
         <v>8</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>88</v>
+        <v>168</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3557,10 +3809,10 @@
         <v>9</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>90</v>
+        <v>170</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3575,10 +3827,10 @@
         <v>10</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>92</v>
+        <v>172</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -3593,10 +3845,10 @@
         <v>1</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>94</v>
+        <v>175</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3611,10 +3863,10 @@
         <v>2</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>96</v>
+        <v>177</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -3629,10 +3881,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>98</v>
+        <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -3647,10 +3899,10 @@
         <v>4</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>100</v>
+        <v>181</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3665,10 +3917,10 @@
         <v>5</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>102</v>
+        <v>183</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -3683,10 +3935,10 @@
         <v>6</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -3701,10 +3953,10 @@
         <v>7</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>106</v>
+        <v>187</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3719,10 +3971,10 @@
         <v>8</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -3737,10 +3989,10 @@
         <v>9</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>110</v>
+        <v>191</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3755,10 +4007,10 @@
         <v>10</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>112</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3773,10 +4025,10 @@
         <v>1</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>194</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -3791,10 +4043,10 @@
         <v>2</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>16</v>
+        <v>196</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3809,10 +4061,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>18</v>
+        <v>198</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3827,10 +4079,10 @@
         <v>4</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>20</v>
+        <v>200</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3845,10 +4097,10 @@
         <v>5</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>22</v>
+        <v>202</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3863,10 +4115,10 @@
         <v>6</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>24</v>
+        <v>204</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3881,10 +4133,10 @@
         <v>7</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>26</v>
+        <v>206</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3899,10 +4151,10 @@
         <v>8</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>28</v>
+        <v>208</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3917,10 +4169,10 @@
         <v>9</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>30</v>
+        <v>210</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3935,10 +4187,10 @@
         <v>10</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>32</v>
+        <v>212</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3953,10 +4205,10 @@
         <v>1</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>34</v>
+        <v>215</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3971,10 +4223,10 @@
         <v>2</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>36</v>
+        <v>217</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3989,10 +4241,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>38</v>
+        <v>219</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -4007,10 +4259,10 @@
         <v>4</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>40</v>
+        <v>221</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -4025,10 +4277,10 @@
         <v>5</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>42</v>
+        <v>223</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4043,10 +4295,10 @@
         <v>6</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>178</v>
+        <v>224</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -4061,10 +4313,10 @@
         <v>7</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>46</v>
+        <v>227</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4079,10 +4331,10 @@
         <v>8</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>48</v>
+        <v>229</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -4097,10 +4349,10 @@
         <v>9</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>181</v>
+        <v>230</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>50</v>
+        <v>231</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -4115,10 +4367,10 @@
         <v>10</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>182</v>
+        <v>232</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>52</v>
+        <v>233</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -4133,10 +4385,10 @@
         <v>1</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>54</v>
+        <v>234</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -4151,10 +4403,10 @@
         <v>2</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>56</v>
+        <v>236</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -4169,10 +4421,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>58</v>
+        <v>238</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -4187,10 +4439,10 @@
         <v>4</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>60</v>
+        <v>240</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -4205,10 +4457,10 @@
         <v>5</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>62</v>
+        <v>242</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -4223,10 +4475,10 @@
         <v>6</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>64</v>
+        <v>244</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -4241,10 +4493,10 @@
         <v>7</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>66</v>
+        <v>246</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -4259,10 +4511,10 @@
         <v>8</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>68</v>
+        <v>248</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -4277,10 +4529,10 @@
         <v>9</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>70</v>
+        <v>250</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -4295,10 +4547,10 @@
         <v>10</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>72</v>
+        <v>252</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -4313,10 +4565,10 @@
         <v>1</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>74</v>
+        <v>255</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -4331,10 +4583,10 @@
         <v>2</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>194</v>
+        <v>256</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>76</v>
+        <v>257</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -4349,10 +4601,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>195</v>
+        <v>258</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>78</v>
+        <v>259</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -4367,10 +4619,10 @@
         <v>4</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>196</v>
+        <v>260</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>80</v>
+        <v>261</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -4385,10 +4637,10 @@
         <v>5</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>82</v>
+        <v>263</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -4403,10 +4655,10 @@
         <v>6</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>198</v>
+        <v>264</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>84</v>
+        <v>265</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -4421,10 +4673,10 @@
         <v>7</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>199</v>
+        <v>266</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>86</v>
+        <v>267</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -4439,10 +4691,10 @@
         <v>8</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>88</v>
+        <v>269</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -4457,10 +4709,10 @@
         <v>9</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>201</v>
+        <v>270</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>90</v>
+        <v>271</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -4475,10 +4727,10 @@
         <v>10</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>92</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -4493,10 +4745,10 @@
         <v>1</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>94</v>
+        <v>274</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -4511,10 +4763,10 @@
         <v>2</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>96</v>
+        <v>276</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -4529,10 +4781,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>98</v>
+        <v>278</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -4547,10 +4799,10 @@
         <v>4</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>100</v>
+        <v>280</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -4565,10 +4817,10 @@
         <v>5</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>102</v>
+        <v>282</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -4583,10 +4835,10 @@
         <v>6</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>104</v>
+        <v>284</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -4601,10 +4853,10 @@
         <v>7</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>106</v>
+        <v>286</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -4619,10 +4871,10 @@
         <v>8</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>108</v>
+        <v>288</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -4637,10 +4889,10 @@
         <v>9</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>110</v>
+        <v>290</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -4655,10 +4907,2710 @@
         <v>10</v>
       </c>
       <c r="D154" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="1">
+        <f t="shared" ref="A155:A186" si="3">B155*1000+C155</f>
+        <v>101016001</v>
+      </c>
+      <c r="B155" s="1">
+        <v>101016</v>
+      </c>
+      <c r="C155" s="1">
+        <v>1</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="1">
+        <f t="shared" si="3"/>
+        <v>101016002</v>
+      </c>
+      <c r="B156" s="1">
+        <v>101016</v>
+      </c>
+      <c r="C156" s="1">
+        <v>2</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="1">
+        <f t="shared" si="3"/>
+        <v>101016003</v>
+      </c>
+      <c r="B157" s="1">
+        <v>101016</v>
+      </c>
+      <c r="C157" s="1">
+        <v>3</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="1">
+        <f t="shared" si="3"/>
+        <v>101016004</v>
+      </c>
+      <c r="B158" s="1">
+        <v>101016</v>
+      </c>
+      <c r="C158" s="1">
+        <v>4</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="1">
+        <f t="shared" si="3"/>
+        <v>101016005</v>
+      </c>
+      <c r="B159" s="1">
+        <v>101016</v>
+      </c>
+      <c r="C159" s="1">
+        <v>5</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="1">
+        <f t="shared" si="3"/>
+        <v>101016006</v>
+      </c>
+      <c r="B160" s="1">
+        <v>101016</v>
+      </c>
+      <c r="C160" s="1">
+        <v>6</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="1">
+        <f t="shared" si="3"/>
+        <v>101016007</v>
+      </c>
+      <c r="B161" s="1">
+        <v>101016</v>
+      </c>
+      <c r="C161" s="1">
+        <v>7</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="1">
+        <f t="shared" si="3"/>
+        <v>101016008</v>
+      </c>
+      <c r="B162" s="1">
+        <v>101016</v>
+      </c>
+      <c r="C162" s="1">
+        <v>8</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="1">
+        <f t="shared" si="3"/>
+        <v>101016009</v>
+      </c>
+      <c r="B163" s="1">
+        <v>101016</v>
+      </c>
+      <c r="C163" s="1">
+        <v>9</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="1">
+        <f t="shared" si="3"/>
+        <v>101016010</v>
+      </c>
+      <c r="B164" s="1">
+        <v>101016</v>
+      </c>
+      <c r="C164" s="1">
+        <v>10</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="1">
+        <f t="shared" si="3"/>
+        <v>102017001</v>
+      </c>
+      <c r="B165" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C165" s="1">
+        <v>1</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="1">
+        <f t="shared" si="3"/>
+        <v>102017002</v>
+      </c>
+      <c r="B166" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C166" s="1">
+        <v>2</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="1">
+        <f t="shared" si="3"/>
+        <v>102017003</v>
+      </c>
+      <c r="B167" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C167" s="1">
+        <v>3</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="1">
+        <f t="shared" si="3"/>
+        <v>102017004</v>
+      </c>
+      <c r="B168" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C168" s="1">
+        <v>4</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="1">
+        <f t="shared" si="3"/>
+        <v>102017005</v>
+      </c>
+      <c r="B169" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C169" s="1">
+        <v>5</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="1">
+        <f t="shared" si="3"/>
+        <v>102017006</v>
+      </c>
+      <c r="B170" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C170" s="1">
+        <v>6</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="1">
+        <f t="shared" si="3"/>
+        <v>102017007</v>
+      </c>
+      <c r="B171" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C171" s="1">
+        <v>7</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="1">
+        <f t="shared" si="3"/>
+        <v>102017008</v>
+      </c>
+      <c r="B172" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C172" s="1">
+        <v>8</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="1">
+        <f t="shared" si="3"/>
+        <v>102017009</v>
+      </c>
+      <c r="B173" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C173" s="1">
+        <v>9</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="1">
+        <f t="shared" si="3"/>
+        <v>102017010</v>
+      </c>
+      <c r="B174" s="1">
+        <v>102017</v>
+      </c>
+      <c r="C174" s="1">
+        <v>10</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="1">
+        <f t="shared" si="3"/>
+        <v>103018001</v>
+      </c>
+      <c r="B175" s="1">
+        <v>103018</v>
+      </c>
+      <c r="C175" s="1">
+        <v>1</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="1">
+        <f t="shared" si="3"/>
+        <v>103018002</v>
+      </c>
+      <c r="B176" s="1">
+        <v>103018</v>
+      </c>
+      <c r="C176" s="1">
+        <v>2</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="1">
+        <f t="shared" si="3"/>
+        <v>103018003</v>
+      </c>
+      <c r="B177" s="1">
+        <v>103018</v>
+      </c>
+      <c r="C177" s="1">
+        <v>3</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="1">
+        <f t="shared" si="3"/>
+        <v>103018004</v>
+      </c>
+      <c r="B178" s="1">
+        <v>103018</v>
+      </c>
+      <c r="C178" s="1">
+        <v>4</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="1">
+        <f t="shared" si="3"/>
+        <v>103018005</v>
+      </c>
+      <c r="B179" s="1">
+        <v>103018</v>
+      </c>
+      <c r="C179" s="1">
+        <v>5</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="1">
+        <f t="shared" si="3"/>
+        <v>103018006</v>
+      </c>
+      <c r="B180" s="1">
+        <v>103018</v>
+      </c>
+      <c r="C180" s="1">
+        <v>6</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="1">
+        <f t="shared" si="3"/>
+        <v>103018007</v>
+      </c>
+      <c r="B181" s="1">
+        <v>103018</v>
+      </c>
+      <c r="C181" s="1">
+        <v>7</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="1">
+        <f t="shared" si="3"/>
+        <v>103018008</v>
+      </c>
+      <c r="B182" s="1">
+        <v>103018</v>
+      </c>
+      <c r="C182" s="1">
+        <v>8</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="1">
+        <f t="shared" si="3"/>
+        <v>103018009</v>
+      </c>
+      <c r="B183" s="1">
+        <v>103018</v>
+      </c>
+      <c r="C183" s="1">
+        <v>9</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="1">
+        <f t="shared" si="3"/>
+        <v>103018010</v>
+      </c>
+      <c r="B184" s="1">
+        <v>103018</v>
+      </c>
+      <c r="C184" s="1">
+        <v>10</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="1">
+        <f t="shared" si="3"/>
+        <v>104019001</v>
+      </c>
+      <c r="B185" s="1">
+        <v>104019</v>
+      </c>
+      <c r="C185" s="1">
+        <v>1</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="1">
+        <f t="shared" si="3"/>
+        <v>104019002</v>
+      </c>
+      <c r="B186" s="1">
+        <v>104019</v>
+      </c>
+      <c r="C186" s="1">
+        <v>2</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="1">
+        <f t="shared" ref="A187:A218" si="4">B187*1000+C187</f>
+        <v>104019003</v>
+      </c>
+      <c r="B187" s="1">
+        <v>104019</v>
+      </c>
+      <c r="C187" s="1">
+        <v>3</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="1">
+        <f t="shared" si="4"/>
+        <v>104019004</v>
+      </c>
+      <c r="B188" s="1">
+        <v>104019</v>
+      </c>
+      <c r="C188" s="1">
+        <v>4</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="1">
+        <f t="shared" si="4"/>
+        <v>104019005</v>
+      </c>
+      <c r="B189" s="1">
+        <v>104019</v>
+      </c>
+      <c r="C189" s="1">
+        <v>5</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="1">
+        <f t="shared" si="4"/>
+        <v>104019006</v>
+      </c>
+      <c r="B190" s="1">
+        <v>104019</v>
+      </c>
+      <c r="C190" s="1">
+        <v>6</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="1">
+        <f t="shared" si="4"/>
+        <v>104019007</v>
+      </c>
+      <c r="B191" s="1">
+        <v>104019</v>
+      </c>
+      <c r="C191" s="1">
+        <v>7</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="1">
+        <f t="shared" si="4"/>
+        <v>104019008</v>
+      </c>
+      <c r="B192" s="1">
+        <v>104019</v>
+      </c>
+      <c r="C192" s="1">
+        <v>8</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="1">
+        <f t="shared" si="4"/>
+        <v>104019009</v>
+      </c>
+      <c r="B193" s="1">
+        <v>104019</v>
+      </c>
+      <c r="C193" s="1">
+        <v>9</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="1">
+        <f t="shared" si="4"/>
+        <v>104019010</v>
+      </c>
+      <c r="B194" s="1">
+        <v>104019</v>
+      </c>
+      <c r="C194" s="1">
+        <v>10</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="1">
+        <f t="shared" si="4"/>
+        <v>105020001</v>
+      </c>
+      <c r="B195" s="1">
+        <v>105020</v>
+      </c>
+      <c r="C195" s="1">
+        <v>1</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="1">
+        <f t="shared" si="4"/>
+        <v>105020002</v>
+      </c>
+      <c r="B196" s="1">
+        <v>105020</v>
+      </c>
+      <c r="C196" s="1">
+        <v>2</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E196" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="1">
+        <f t="shared" si="4"/>
+        <v>105020003</v>
+      </c>
+      <c r="B197" s="1">
+        <v>105020</v>
+      </c>
+      <c r="C197" s="1">
+        <v>3</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E197" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="1">
+        <f t="shared" si="4"/>
+        <v>105020004</v>
+      </c>
+      <c r="B198" s="1">
+        <v>105020</v>
+      </c>
+      <c r="C198" s="1">
+        <v>4</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E198" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="1">
+        <f t="shared" si="4"/>
+        <v>105020005</v>
+      </c>
+      <c r="B199" s="1">
+        <v>105020</v>
+      </c>
+      <c r="C199" s="1">
+        <v>5</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E199" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="1">
+        <f t="shared" si="4"/>
+        <v>105020006</v>
+      </c>
+      <c r="B200" s="1">
+        <v>105020</v>
+      </c>
+      <c r="C200" s="1">
+        <v>6</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E200" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="1">
+        <f t="shared" si="4"/>
+        <v>105020007</v>
+      </c>
+      <c r="B201" s="1">
+        <v>105020</v>
+      </c>
+      <c r="C201" s="1">
+        <v>7</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E201" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="1">
+        <f t="shared" si="4"/>
+        <v>105020008</v>
+      </c>
+      <c r="B202" s="1">
+        <v>105020</v>
+      </c>
+      <c r="C202" s="1">
+        <v>8</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E202" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="1">
+        <f t="shared" si="4"/>
+        <v>105020009</v>
+      </c>
+      <c r="B203" s="1">
+        <v>105020</v>
+      </c>
+      <c r="C203" s="1">
+        <v>9</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E203" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="1">
+        <f t="shared" si="4"/>
+        <v>105020010</v>
+      </c>
+      <c r="B204" s="1">
+        <v>105020</v>
+      </c>
+      <c r="C204" s="1">
+        <v>10</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E204" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="1">
+        <f t="shared" si="4"/>
+        <v>201021001</v>
+      </c>
+      <c r="B205" s="1">
+        <v>201021</v>
+      </c>
+      <c r="C205" s="1">
+        <v>1</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="1">
+        <f t="shared" si="4"/>
+        <v>201021002</v>
+      </c>
+      <c r="B206" s="1">
+        <v>201021</v>
+      </c>
+      <c r="C206" s="1">
+        <v>2</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="1">
+        <f t="shared" si="4"/>
+        <v>201021003</v>
+      </c>
+      <c r="B207" s="1">
+        <v>201021</v>
+      </c>
+      <c r="C207" s="1">
+        <v>3</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="1">
+        <f t="shared" si="4"/>
+        <v>201021004</v>
+      </c>
+      <c r="B208" s="1">
+        <v>201021</v>
+      </c>
+      <c r="C208" s="1">
+        <v>4</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="1">
+        <f t="shared" si="4"/>
+        <v>201021005</v>
+      </c>
+      <c r="B209" s="1">
+        <v>201021</v>
+      </c>
+      <c r="C209" s="1">
+        <v>5</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="1">
+        <f t="shared" si="4"/>
+        <v>201021006</v>
+      </c>
+      <c r="B210" s="1">
+        <v>201021</v>
+      </c>
+      <c r="C210" s="1">
+        <v>6</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="1">
+        <f t="shared" si="4"/>
+        <v>201021007</v>
+      </c>
+      <c r="B211" s="1">
+        <v>201021</v>
+      </c>
+      <c r="C211" s="1">
+        <v>7</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="1">
+        <f t="shared" si="4"/>
+        <v>201021008</v>
+      </c>
+      <c r="B212" s="1">
+        <v>201021</v>
+      </c>
+      <c r="C212" s="1">
+        <v>8</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="1">
+        <f t="shared" si="4"/>
+        <v>201021009</v>
+      </c>
+      <c r="B213" s="1">
+        <v>201021</v>
+      </c>
+      <c r="C213" s="1">
+        <v>9</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="1">
+        <f t="shared" si="4"/>
+        <v>201021010</v>
+      </c>
+      <c r="B214" s="1">
+        <v>201021</v>
+      </c>
+      <c r="C214" s="1">
+        <v>10</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="1">
+        <f t="shared" si="4"/>
+        <v>202022001</v>
+      </c>
+      <c r="B215" s="1">
+        <v>202022</v>
+      </c>
+      <c r="C215" s="1">
+        <v>1</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="1">
+        <f t="shared" si="4"/>
+        <v>202022002</v>
+      </c>
+      <c r="B216" s="1">
+        <v>202022</v>
+      </c>
+      <c r="C216" s="1">
+        <v>2</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="1">
+        <f t="shared" si="4"/>
+        <v>202022003</v>
+      </c>
+      <c r="B217" s="1">
+        <v>202022</v>
+      </c>
+      <c r="C217" s="1">
+        <v>3</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E217" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="1">
+        <f t="shared" si="4"/>
+        <v>202022004</v>
+      </c>
+      <c r="B218" s="1">
+        <v>202022</v>
+      </c>
+      <c r="C218" s="1">
+        <v>4</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="1">
+        <f t="shared" ref="A219:A250" si="5">B219*1000+C219</f>
+        <v>202022005</v>
+      </c>
+      <c r="B219" s="1">
+        <v>202022</v>
+      </c>
+      <c r="C219" s="1">
+        <v>5</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E219" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="1">
+        <f t="shared" si="5"/>
+        <v>202022006</v>
+      </c>
+      <c r="B220" s="1">
+        <v>202022</v>
+      </c>
+      <c r="C220" s="1">
+        <v>6</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="1">
+        <f t="shared" si="5"/>
+        <v>202022007</v>
+      </c>
+      <c r="B221" s="1">
+        <v>202022</v>
+      </c>
+      <c r="C221" s="1">
+        <v>7</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="1">
+        <f t="shared" si="5"/>
+        <v>202022008</v>
+      </c>
+      <c r="B222" s="1">
+        <v>202022</v>
+      </c>
+      <c r="C222" s="1">
+        <v>8</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="1">
+        <f t="shared" si="5"/>
+        <v>202022009</v>
+      </c>
+      <c r="B223" s="1">
+        <v>202022</v>
+      </c>
+      <c r="C223" s="1">
+        <v>9</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E223" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="1">
+        <f t="shared" si="5"/>
+        <v>202022010</v>
+      </c>
+      <c r="B224" s="1">
+        <v>202022</v>
+      </c>
+      <c r="C224" s="1">
+        <v>10</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E224" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="1">
+        <f t="shared" si="5"/>
+        <v>203023001</v>
+      </c>
+      <c r="B225" s="1">
+        <v>203023</v>
+      </c>
+      <c r="C225" s="1">
+        <v>1</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="1">
+        <f t="shared" si="5"/>
+        <v>203023002</v>
+      </c>
+      <c r="B226" s="1">
+        <v>203023</v>
+      </c>
+      <c r="C226" s="1">
+        <v>2</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="1">
+        <f t="shared" si="5"/>
+        <v>203023003</v>
+      </c>
+      <c r="B227" s="1">
+        <v>203023</v>
+      </c>
+      <c r="C227" s="1">
+        <v>3</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="1">
+        <f t="shared" si="5"/>
+        <v>203023004</v>
+      </c>
+      <c r="B228" s="1">
+        <v>203023</v>
+      </c>
+      <c r="C228" s="1">
+        <v>4</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="1">
+        <f t="shared" si="5"/>
+        <v>203023005</v>
+      </c>
+      <c r="B229" s="1">
+        <v>203023</v>
+      </c>
+      <c r="C229" s="1">
+        <v>5</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="1">
+        <f t="shared" si="5"/>
+        <v>203023006</v>
+      </c>
+      <c r="B230" s="1">
+        <v>203023</v>
+      </c>
+      <c r="C230" s="1">
+        <v>6</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="1">
+        <f t="shared" si="5"/>
+        <v>203023007</v>
+      </c>
+      <c r="B231" s="1">
+        <v>203023</v>
+      </c>
+      <c r="C231" s="1">
+        <v>7</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="1">
+        <f t="shared" si="5"/>
+        <v>203023008</v>
+      </c>
+      <c r="B232" s="1">
+        <v>203023</v>
+      </c>
+      <c r="C232" s="1">
+        <v>8</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="1">
+        <f t="shared" si="5"/>
+        <v>203023009</v>
+      </c>
+      <c r="B233" s="1">
+        <v>203023</v>
+      </c>
+      <c r="C233" s="1">
+        <v>9</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="1">
+        <f t="shared" si="5"/>
+        <v>203023010</v>
+      </c>
+      <c r="B234" s="1">
+        <v>203023</v>
+      </c>
+      <c r="C234" s="1">
+        <v>10</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="1">
+        <f t="shared" si="5"/>
+        <v>204024001</v>
+      </c>
+      <c r="B235" s="1">
+        <v>204024</v>
+      </c>
+      <c r="C235" s="1">
+        <v>1</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E235" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="1">
+        <f t="shared" si="5"/>
+        <v>204024002</v>
+      </c>
+      <c r="B236" s="1">
+        <v>204024</v>
+      </c>
+      <c r="C236" s="1">
+        <v>2</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E236" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="1">
+        <f t="shared" si="5"/>
+        <v>204024003</v>
+      </c>
+      <c r="B237" s="1">
+        <v>204024</v>
+      </c>
+      <c r="C237" s="1">
+        <v>3</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E237" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="1">
+        <f t="shared" si="5"/>
+        <v>204024004</v>
+      </c>
+      <c r="B238" s="1">
+        <v>204024</v>
+      </c>
+      <c r="C238" s="1">
+        <v>4</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E238" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="1">
+        <f t="shared" si="5"/>
+        <v>204024005</v>
+      </c>
+      <c r="B239" s="1">
+        <v>204024</v>
+      </c>
+      <c r="C239" s="1">
+        <v>5</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E239" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="1">
+        <f t="shared" si="5"/>
+        <v>204024006</v>
+      </c>
+      <c r="B240" s="1">
+        <v>204024</v>
+      </c>
+      <c r="C240" s="1">
+        <v>6</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E240" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="1">
+        <f t="shared" si="5"/>
+        <v>204024007</v>
+      </c>
+      <c r="B241" s="1">
+        <v>204024</v>
+      </c>
+      <c r="C241" s="1">
+        <v>7</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E241" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="1">
+        <f t="shared" si="5"/>
+        <v>204024008</v>
+      </c>
+      <c r="B242" s="1">
+        <v>204024</v>
+      </c>
+      <c r="C242" s="1">
+        <v>8</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E242" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="1">
+        <f t="shared" si="5"/>
+        <v>204024009</v>
+      </c>
+      <c r="B243" s="1">
+        <v>204024</v>
+      </c>
+      <c r="C243" s="1">
+        <v>9</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E243" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="1">
+        <f t="shared" si="5"/>
+        <v>204024010</v>
+      </c>
+      <c r="B244" s="1">
+        <v>204024</v>
+      </c>
+      <c r="C244" s="1">
+        <v>10</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E244" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="1">
+        <f t="shared" si="5"/>
+        <v>205025001</v>
+      </c>
+      <c r="B245" s="1">
+        <v>205025</v>
+      </c>
+      <c r="C245" s="1">
+        <v>1</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="1">
+        <f t="shared" si="5"/>
+        <v>205025002</v>
+      </c>
+      <c r="B246" s="1">
+        <v>205025</v>
+      </c>
+      <c r="C246" s="1">
+        <v>2</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="1">
+        <f t="shared" si="5"/>
+        <v>205025003</v>
+      </c>
+      <c r="B247" s="1">
+        <v>205025</v>
+      </c>
+      <c r="C247" s="1">
+        <v>3</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="1">
+        <f t="shared" si="5"/>
+        <v>205025004</v>
+      </c>
+      <c r="B248" s="1">
+        <v>205025</v>
+      </c>
+      <c r="C248" s="1">
+        <v>4</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="1">
+        <f t="shared" si="5"/>
+        <v>205025005</v>
+      </c>
+      <c r="B249" s="1">
+        <v>205025</v>
+      </c>
+      <c r="C249" s="1">
+        <v>5</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="1">
+        <f t="shared" si="5"/>
+        <v>205025006</v>
+      </c>
+      <c r="B250" s="1">
+        <v>205025</v>
+      </c>
+      <c r="C250" s="1">
+        <v>6</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="1">
+        <f t="shared" ref="A251:A282" si="6">B251*1000+C251</f>
+        <v>205025007</v>
+      </c>
+      <c r="B251" s="1">
+        <v>205025</v>
+      </c>
+      <c r="C251" s="1">
+        <v>7</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="1">
+        <f t="shared" si="6"/>
+        <v>205025008</v>
+      </c>
+      <c r="B252" s="1">
+        <v>205025</v>
+      </c>
+      <c r="C252" s="1">
+        <v>8</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="1">
+        <f t="shared" si="6"/>
+        <v>205025009</v>
+      </c>
+      <c r="B253" s="1">
+        <v>205025</v>
+      </c>
+      <c r="C253" s="1">
+        <v>9</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="1">
+        <f t="shared" si="6"/>
+        <v>205025010</v>
+      </c>
+      <c r="B254" s="1">
+        <v>205025</v>
+      </c>
+      <c r="C254" s="1">
+        <v>10</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="1">
+        <f t="shared" si="6"/>
+        <v>301026001</v>
+      </c>
+      <c r="B255" s="1">
+        <v>301026</v>
+      </c>
+      <c r="C255" s="1">
+        <v>1</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E255" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="1">
+        <f t="shared" si="6"/>
+        <v>301026002</v>
+      </c>
+      <c r="B256" s="1">
+        <v>301026</v>
+      </c>
+      <c r="C256" s="1">
+        <v>2</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E256" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="1">
+        <f t="shared" si="6"/>
+        <v>301026003</v>
+      </c>
+      <c r="B257" s="1">
+        <v>301026</v>
+      </c>
+      <c r="C257" s="1">
+        <v>3</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E257" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="1">
+        <f t="shared" si="6"/>
+        <v>301026004</v>
+      </c>
+      <c r="B258" s="1">
+        <v>301026</v>
+      </c>
+      <c r="C258" s="1">
+        <v>4</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E258" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="1">
+        <f t="shared" si="6"/>
+        <v>301026005</v>
+      </c>
+      <c r="B259" s="1">
+        <v>301026</v>
+      </c>
+      <c r="C259" s="1">
+        <v>5</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E259" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="1">
+        <f t="shared" si="6"/>
+        <v>301026006</v>
+      </c>
+      <c r="B260" s="1">
+        <v>301026</v>
+      </c>
+      <c r="C260" s="1">
+        <v>6</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E260" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="1">
+        <f t="shared" si="6"/>
+        <v>301026007</v>
+      </c>
+      <c r="B261" s="1">
+        <v>301026</v>
+      </c>
+      <c r="C261" s="1">
+        <v>7</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="1">
+        <f t="shared" si="6"/>
+        <v>301026008</v>
+      </c>
+      <c r="B262" s="1">
+        <v>301026</v>
+      </c>
+      <c r="C262" s="1">
+        <v>8</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="1">
+        <f t="shared" si="6"/>
+        <v>301026009</v>
+      </c>
+      <c r="B263" s="1">
+        <v>301026</v>
+      </c>
+      <c r="C263" s="1">
+        <v>9</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E263" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="1">
+        <f t="shared" si="6"/>
+        <v>301026010</v>
+      </c>
+      <c r="B264" s="1">
+        <v>301026</v>
+      </c>
+      <c r="C264" s="1">
+        <v>10</v>
+      </c>
+      <c r="D264" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E154" s="1" t="s">
-        <v>112</v>
+      <c r="E264" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="1">
+        <f t="shared" si="6"/>
+        <v>302027001</v>
+      </c>
+      <c r="B265" s="1">
+        <v>302027</v>
+      </c>
+      <c r="C265" s="1">
+        <v>1</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="1">
+        <f t="shared" si="6"/>
+        <v>302027002</v>
+      </c>
+      <c r="B266" s="1">
+        <v>302027</v>
+      </c>
+      <c r="C266" s="1">
+        <v>2</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="1">
+        <f t="shared" si="6"/>
+        <v>302027003</v>
+      </c>
+      <c r="B267" s="1">
+        <v>302027</v>
+      </c>
+      <c r="C267" s="1">
+        <v>3</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="1">
+        <f t="shared" si="6"/>
+        <v>302027004</v>
+      </c>
+      <c r="B268" s="1">
+        <v>302027</v>
+      </c>
+      <c r="C268" s="1">
+        <v>4</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="1">
+        <f t="shared" si="6"/>
+        <v>302027005</v>
+      </c>
+      <c r="B269" s="1">
+        <v>302027</v>
+      </c>
+      <c r="C269" s="1">
+        <v>5</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="1">
+        <f t="shared" si="6"/>
+        <v>302027006</v>
+      </c>
+      <c r="B270" s="1">
+        <v>302027</v>
+      </c>
+      <c r="C270" s="1">
+        <v>6</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="1">
+        <f t="shared" si="6"/>
+        <v>302027007</v>
+      </c>
+      <c r="B271" s="1">
+        <v>302027</v>
+      </c>
+      <c r="C271" s="1">
+        <v>7</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="1">
+        <f t="shared" si="6"/>
+        <v>302027008</v>
+      </c>
+      <c r="B272" s="1">
+        <v>302027</v>
+      </c>
+      <c r="C272" s="1">
+        <v>8</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="1">
+        <f t="shared" si="6"/>
+        <v>302027009</v>
+      </c>
+      <c r="B273" s="1">
+        <v>302027</v>
+      </c>
+      <c r="C273" s="1">
+        <v>9</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="1">
+        <f t="shared" si="6"/>
+        <v>302027010</v>
+      </c>
+      <c r="B274" s="1">
+        <v>302027</v>
+      </c>
+      <c r="C274" s="1">
+        <v>10</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="1">
+        <f t="shared" si="6"/>
+        <v>303028001</v>
+      </c>
+      <c r="B275" s="1">
+        <v>303028</v>
+      </c>
+      <c r="C275" s="1">
+        <v>1</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E275" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="1">
+        <f t="shared" si="6"/>
+        <v>303028002</v>
+      </c>
+      <c r="B276" s="1">
+        <v>303028</v>
+      </c>
+      <c r="C276" s="1">
+        <v>2</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E276" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="1">
+        <f t="shared" si="6"/>
+        <v>303028003</v>
+      </c>
+      <c r="B277" s="1">
+        <v>303028</v>
+      </c>
+      <c r="C277" s="1">
+        <v>3</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E277" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="1">
+        <f t="shared" si="6"/>
+        <v>303028004</v>
+      </c>
+      <c r="B278" s="1">
+        <v>303028</v>
+      </c>
+      <c r="C278" s="1">
+        <v>4</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E278" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="1">
+        <f t="shared" si="6"/>
+        <v>303028005</v>
+      </c>
+      <c r="B279" s="1">
+        <v>303028</v>
+      </c>
+      <c r="C279" s="1">
+        <v>5</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E279" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="1">
+        <f t="shared" si="6"/>
+        <v>303028006</v>
+      </c>
+      <c r="B280" s="1">
+        <v>303028</v>
+      </c>
+      <c r="C280" s="1">
+        <v>6</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E280" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="1">
+        <f t="shared" si="6"/>
+        <v>303028007</v>
+      </c>
+      <c r="B281" s="1">
+        <v>303028</v>
+      </c>
+      <c r="C281" s="1">
+        <v>7</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E281" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="1">
+        <f t="shared" si="6"/>
+        <v>303028008</v>
+      </c>
+      <c r="B282" s="1">
+        <v>303028</v>
+      </c>
+      <c r="C282" s="1">
+        <v>8</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E282" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="1">
+        <f t="shared" ref="A283:A304" si="7">B283*1000+C283</f>
+        <v>303028009</v>
+      </c>
+      <c r="B283" s="1">
+        <v>303028</v>
+      </c>
+      <c r="C283" s="1">
+        <v>9</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E283" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="1">
+        <f t="shared" si="7"/>
+        <v>303028010</v>
+      </c>
+      <c r="B284" s="1">
+        <v>303028</v>
+      </c>
+      <c r="C284" s="1">
+        <v>10</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E284" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="1">
+        <f t="shared" si="7"/>
+        <v>304029001</v>
+      </c>
+      <c r="B285" s="1">
+        <v>304029</v>
+      </c>
+      <c r="C285" s="1">
+        <v>1</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="1">
+        <f t="shared" si="7"/>
+        <v>304029002</v>
+      </c>
+      <c r="B286" s="1">
+        <v>304029</v>
+      </c>
+      <c r="C286" s="1">
+        <v>2</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="1">
+        <f t="shared" si="7"/>
+        <v>304029003</v>
+      </c>
+      <c r="B287" s="1">
+        <v>304029</v>
+      </c>
+      <c r="C287" s="1">
+        <v>3</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="1">
+        <f t="shared" si="7"/>
+        <v>304029004</v>
+      </c>
+      <c r="B288" s="1">
+        <v>304029</v>
+      </c>
+      <c r="C288" s="1">
+        <v>4</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="1">
+        <f t="shared" si="7"/>
+        <v>304029005</v>
+      </c>
+      <c r="B289" s="1">
+        <v>304029</v>
+      </c>
+      <c r="C289" s="1">
+        <v>5</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="1">
+        <f t="shared" si="7"/>
+        <v>304029006</v>
+      </c>
+      <c r="B290" s="1">
+        <v>304029</v>
+      </c>
+      <c r="C290" s="1">
+        <v>6</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="1">
+        <f t="shared" si="7"/>
+        <v>304029007</v>
+      </c>
+      <c r="B291" s="1">
+        <v>304029</v>
+      </c>
+      <c r="C291" s="1">
+        <v>7</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="1">
+        <f t="shared" si="7"/>
+        <v>304029008</v>
+      </c>
+      <c r="B292" s="1">
+        <v>304029</v>
+      </c>
+      <c r="C292" s="1">
+        <v>8</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="1">
+        <f t="shared" si="7"/>
+        <v>304029009</v>
+      </c>
+      <c r="B293" s="1">
+        <v>304029</v>
+      </c>
+      <c r="C293" s="1">
+        <v>9</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="1">
+        <f t="shared" si="7"/>
+        <v>304029010</v>
+      </c>
+      <c r="B294" s="1">
+        <v>304029</v>
+      </c>
+      <c r="C294" s="1">
+        <v>10</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="1">
+        <f t="shared" si="7"/>
+        <v>305030001</v>
+      </c>
+      <c r="B295" s="1">
+        <v>305030</v>
+      </c>
+      <c r="C295" s="1">
+        <v>1</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E295" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="1">
+        <f t="shared" si="7"/>
+        <v>305030002</v>
+      </c>
+      <c r="B296" s="1">
+        <v>305030</v>
+      </c>
+      <c r="C296" s="1">
+        <v>2</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E296" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="1">
+        <f t="shared" si="7"/>
+        <v>305030003</v>
+      </c>
+      <c r="B297" s="1">
+        <v>305030</v>
+      </c>
+      <c r="C297" s="1">
+        <v>3</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E297" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="1">
+        <f t="shared" si="7"/>
+        <v>305030004</v>
+      </c>
+      <c r="B298" s="1">
+        <v>305030</v>
+      </c>
+      <c r="C298" s="1">
+        <v>4</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E298" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="1">
+        <f t="shared" si="7"/>
+        <v>305030005</v>
+      </c>
+      <c r="B299" s="1">
+        <v>305030</v>
+      </c>
+      <c r="C299" s="1">
+        <v>5</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E299" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="1">
+        <f t="shared" si="7"/>
+        <v>305030006</v>
+      </c>
+      <c r="B300" s="1">
+        <v>305030</v>
+      </c>
+      <c r="C300" s="1">
+        <v>6</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E300" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="1">
+        <f t="shared" si="7"/>
+        <v>305030007</v>
+      </c>
+      <c r="B301" s="1">
+        <v>305030</v>
+      </c>
+      <c r="C301" s="1">
+        <v>7</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E301" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="1">
+        <f t="shared" si="7"/>
+        <v>305030008</v>
+      </c>
+      <c r="B302" s="1">
+        <v>305030</v>
+      </c>
+      <c r="C302" s="1">
+        <v>8</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E302" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="1">
+        <f t="shared" si="7"/>
+        <v>305030009</v>
+      </c>
+      <c r="B303" s="1">
+        <v>305030</v>
+      </c>
+      <c r="C303" s="1">
+        <v>9</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E303" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="1">
+        <f t="shared" si="7"/>
+        <v>305030010</v>
+      </c>
+      <c r="B304" s="1">
+        <v>305030</v>
+      </c>
+      <c r="C304" s="1">
+        <v>10</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E304" s="6" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/EmployeeLevel.xlsx
+++ b/hall/resources/sample/EmployeeLevel.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="EmployeeLevel" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,11 +51,14 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1-知名度
-2-服务能力
-3-游戏属性
-4-管理属性
-5-服务属性</t>
+对应BuildingAreaTable配置表中的建筑属性分类字段；
+1. 建筑产金币
+2. 建筑产能量
+3. 服务能力
+4. 游戏上限
+5. 知名度
+6. 曝光度
+</t>
         </r>
       </text>
     </comment>
@@ -107,61 +111,61 @@
     <t>1024008_1000</t>
   </si>
   <si>
-    <t>3_100</t>
+    <t>1_100</t>
   </si>
   <si>
     <t>1024008_1100</t>
   </si>
   <si>
-    <t>3_200</t>
+    <t>1_200</t>
   </si>
   <si>
     <t>1024008_1200</t>
   </si>
   <si>
-    <t>3_300</t>
+    <t>1_300</t>
   </si>
   <si>
     <t>1024008_1300</t>
   </si>
   <si>
-    <t>3_400</t>
+    <t>1_400</t>
   </si>
   <si>
     <t>1024008_1400</t>
   </si>
   <si>
-    <t>3_500</t>
+    <t>1_500</t>
   </si>
   <si>
     <t>1024008_1500</t>
   </si>
   <si>
-    <t>3_600</t>
+    <t>1_600</t>
   </si>
   <si>
     <t>1024008_1600</t>
   </si>
   <si>
-    <t>3_700</t>
+    <t>1_700</t>
   </si>
   <si>
     <t>1024008_1700</t>
   </si>
   <si>
-    <t>3_800</t>
+    <t>1_800</t>
   </si>
   <si>
     <t>1024008_1800</t>
   </si>
   <si>
-    <t>3_900</t>
+    <t>1_900</t>
   </si>
   <si>
     <t>1024008_1900</t>
   </si>
   <si>
-    <t>3_2000</t>
+    <t>1_2000</t>
   </si>
   <si>
     <t>1024008_5000</t>
@@ -176,31 +180,31 @@
     <t>1024008_5300</t>
   </si>
   <si>
-    <t>3_1000</t>
+    <t>1_1000</t>
   </si>
   <si>
     <t>1024008_5400</t>
   </si>
   <si>
-    <t>3_1200</t>
+    <t>1_1200</t>
   </si>
   <si>
     <t>1024008_5500</t>
   </si>
   <si>
-    <t>3_1400</t>
+    <t>1_1400</t>
   </si>
   <si>
     <t>1024008_5600</t>
   </si>
   <si>
-    <t>3_1600</t>
+    <t>1_1600</t>
   </si>
   <si>
     <t>1024008_5700</t>
   </si>
   <si>
-    <t>3_1800</t>
+    <t>1_1800</t>
   </si>
   <si>
     <t>1024008_5800</t>
@@ -209,7 +213,7 @@
     <t>1024008_5900</t>
   </si>
   <si>
-    <t>3_3000</t>
+    <t>1_3000</t>
   </si>
   <si>
     <t>1024008_10000</t>
@@ -221,7 +225,7 @@
     <t>1024008_10200</t>
   </si>
   <si>
-    <t>3_1100</t>
+    <t>1_1100</t>
   </si>
   <si>
     <t>1024008_10300</t>
@@ -230,7 +234,7 @@
     <t>1024008_10400</t>
   </si>
   <si>
-    <t>3_1700</t>
+    <t>1_1700</t>
   </si>
   <si>
     <t>1024008_10500</t>
@@ -239,25 +243,25 @@
     <t>1024008_10600</t>
   </si>
   <si>
-    <t>3_2300</t>
+    <t>1_2300</t>
   </si>
   <si>
     <t>1024008_10700</t>
   </si>
   <si>
-    <t>3_2600</t>
+    <t>1_2600</t>
   </si>
   <si>
     <t>1024008_10800</t>
   </si>
   <si>
-    <t>3_2900</t>
+    <t>1_2900</t>
   </si>
   <si>
     <t>1024008_10900</t>
   </si>
   <si>
-    <t>3_4000</t>
+    <t>1_4000</t>
   </si>
   <si>
     <t>1024008_15000</t>
@@ -275,7 +279,7 @@
     <t>1024008_15400</t>
   </si>
   <si>
-    <t>3_2200</t>
+    <t>1_2200</t>
   </si>
   <si>
     <t>1024008_15500</t>
@@ -287,19 +291,19 @@
     <t>1024008_15700</t>
   </si>
   <si>
-    <t>3_3400</t>
+    <t>1_3400</t>
   </si>
   <si>
     <t>1024008_15800</t>
   </si>
   <si>
-    <t>3_3800</t>
+    <t>1_3800</t>
   </si>
   <si>
     <t>1024008_15900</t>
   </si>
   <si>
-    <t>3_5000</t>
+    <t>1_5000</t>
   </si>
   <si>
     <t>1024008_20000</t>
@@ -308,7 +312,7 @@
     <t>1024008_20100</t>
   </si>
   <si>
-    <t>3_1500</t>
+    <t>1_1500</t>
   </si>
   <si>
     <t>1024008_20200</t>
@@ -317,7 +321,7 @@
     <t>1024008_20300</t>
   </si>
   <si>
-    <t>3_2500</t>
+    <t>1_2500</t>
   </si>
   <si>
     <t>1024008_20400</t>
@@ -326,7 +330,7 @@
     <t>1024008_20500</t>
   </si>
   <si>
-    <t>3_3500</t>
+    <t>1_3500</t>
   </si>
   <si>
     <t>1024008_20600</t>
@@ -335,7 +339,7 @@
     <t>1024008_20700</t>
   </si>
   <si>
-    <t>3_4500</t>
+    <t>1_4500</t>
   </si>
   <si>
     <t>1024008_20800</t>
@@ -344,607 +348,607 @@
     <t>1024008_20900</t>
   </si>
   <si>
-    <t>3_8000</t>
+    <t>1_8000</t>
   </si>
   <si>
     <t>1024009_1000</t>
   </si>
   <si>
-    <t>5_100</t>
+    <t>2_100</t>
   </si>
   <si>
     <t>1024009_1100</t>
   </si>
   <si>
-    <t>5_110</t>
+    <t>2_110</t>
   </si>
   <si>
     <t>1024009_1200</t>
   </si>
   <si>
-    <t>5_120</t>
+    <t>2_120</t>
   </si>
   <si>
     <t>1024009_1300</t>
   </si>
   <si>
-    <t>5_130</t>
+    <t>2_130</t>
   </si>
   <si>
     <t>1024009_1400</t>
   </si>
   <si>
-    <t>5_140</t>
+    <t>2_140</t>
   </si>
   <si>
     <t>1024009_1500</t>
   </si>
   <si>
-    <t>5_150</t>
+    <t>2_150</t>
   </si>
   <si>
     <t>1024009_1600</t>
   </si>
   <si>
-    <t>5_160</t>
+    <t>2_160</t>
   </si>
   <si>
     <t>1024009_1700</t>
   </si>
   <si>
-    <t>5_170</t>
+    <t>2_170</t>
   </si>
   <si>
     <t>1024009_1800</t>
   </si>
   <si>
-    <t>5_180</t>
+    <t>2_180</t>
   </si>
   <si>
     <t>1024009_1900</t>
   </si>
   <si>
-    <t>5_190</t>
+    <t>2_190</t>
   </si>
   <si>
     <t>1024009_5000</t>
   </si>
   <si>
-    <t>5_200</t>
+    <t>2_200</t>
   </si>
   <si>
     <t>1024009_5100</t>
   </si>
   <si>
-    <t>5_210</t>
+    <t>2_210</t>
   </si>
   <si>
     <t>1024009_5200</t>
   </si>
   <si>
-    <t>5_220</t>
+    <t>2_220</t>
   </si>
   <si>
     <t>1024009_5300</t>
   </si>
   <si>
-    <t>5_230</t>
+    <t>2_230</t>
   </si>
   <si>
     <t>1024009_5400</t>
   </si>
   <si>
-    <t>5_240</t>
+    <t>2_240</t>
   </si>
   <si>
     <t>1024009_5500</t>
   </si>
   <si>
-    <t>5_250</t>
+    <t>2_250</t>
   </si>
   <si>
     <t>1024009_5600</t>
   </si>
   <si>
-    <t>5_260</t>
+    <t>2_260</t>
   </si>
   <si>
     <t>1024009_5700</t>
   </si>
   <si>
-    <t>5_270</t>
+    <t>2_270</t>
   </si>
   <si>
     <t>1024009_5800</t>
   </si>
   <si>
-    <t>5_280</t>
+    <t>2_280</t>
   </si>
   <si>
     <t>1024009_5900</t>
   </si>
   <si>
-    <t>5_290</t>
+    <t>2_290</t>
   </si>
   <si>
     <t>1024009_10000</t>
   </si>
   <si>
-    <t>5_300</t>
+    <t>2_300</t>
   </si>
   <si>
     <t>1024009_10100</t>
   </si>
   <si>
-    <t>5_310</t>
+    <t>2_310</t>
   </si>
   <si>
     <t>1024009_10200</t>
   </si>
   <si>
-    <t>5_320</t>
+    <t>2_320</t>
   </si>
   <si>
     <t>1024009_10300</t>
   </si>
   <si>
-    <t>5_330</t>
+    <t>2_330</t>
   </si>
   <si>
     <t>1024009_10400</t>
   </si>
   <si>
-    <t>5_340</t>
+    <t>2_340</t>
   </si>
   <si>
     <t>1024009_10500</t>
   </si>
   <si>
-    <t>5_350</t>
+    <t>2_350</t>
   </si>
   <si>
     <t>1024009_10600</t>
   </si>
   <si>
-    <t>5_360</t>
+    <t>2_360</t>
   </si>
   <si>
     <t>1024009_10700</t>
   </si>
   <si>
-    <t>5_370</t>
+    <t>2_370</t>
   </si>
   <si>
     <t>1024009_10800</t>
   </si>
   <si>
-    <t>5_380</t>
+    <t>2_380</t>
   </si>
   <si>
     <t>1024009_10900</t>
   </si>
   <si>
-    <t>5_390</t>
+    <t>2_390</t>
   </si>
   <si>
     <t>1024009_15000</t>
   </si>
   <si>
-    <t>5_400</t>
+    <t>2_400</t>
   </si>
   <si>
     <t>1024009_15100</t>
   </si>
   <si>
-    <t>5_410</t>
+    <t>2_410</t>
   </si>
   <si>
     <t>1024009_15200</t>
   </si>
   <si>
-    <t>5_420</t>
+    <t>2_420</t>
   </si>
   <si>
     <t>1024009_15300</t>
   </si>
   <si>
-    <t>5_430</t>
+    <t>2_430</t>
   </si>
   <si>
     <t>1024009_15400</t>
   </si>
   <si>
-    <t>5_440</t>
+    <t>2_440</t>
   </si>
   <si>
     <t>1024009_15500</t>
   </si>
   <si>
-    <t>5_450</t>
+    <t>2_450</t>
   </si>
   <si>
     <t>1024009_15600</t>
   </si>
   <si>
-    <t>5_460</t>
+    <t>2_460</t>
   </si>
   <si>
     <t>1024009_15700</t>
   </si>
   <si>
-    <t>5_470</t>
+    <t>2_470</t>
   </si>
   <si>
     <t>1024009_15800</t>
   </si>
   <si>
-    <t>5_480</t>
+    <t>2_480</t>
   </si>
   <si>
     <t>1024009_15900</t>
   </si>
   <si>
-    <t>5_490</t>
+    <t>2_490</t>
   </si>
   <si>
     <t>1024009_20000</t>
   </si>
   <si>
-    <t>5_500</t>
+    <t>2_500</t>
   </si>
   <si>
     <t>1024009_20100</t>
   </si>
   <si>
-    <t>5_510</t>
+    <t>2_510</t>
   </si>
   <si>
     <t>1024009_20200</t>
   </si>
   <si>
-    <t>5_520</t>
+    <t>2_520</t>
   </si>
   <si>
     <t>1024009_20300</t>
   </si>
   <si>
-    <t>5_530</t>
+    <t>2_530</t>
   </si>
   <si>
     <t>1024009_20400</t>
   </si>
   <si>
-    <t>5_540</t>
+    <t>2_540</t>
   </si>
   <si>
     <t>1024009_20500</t>
   </si>
   <si>
-    <t>5_550</t>
+    <t>2_550</t>
   </si>
   <si>
     <t>1024009_20600</t>
   </si>
   <si>
-    <t>5_560</t>
+    <t>2_560</t>
   </si>
   <si>
     <t>1024009_20700</t>
   </si>
   <si>
-    <t>5_570</t>
+    <t>2_570</t>
   </si>
   <si>
     <t>1024009_20800</t>
   </si>
   <si>
-    <t>5_580</t>
+    <t>2_580</t>
   </si>
   <si>
     <t>1024009_20900</t>
   </si>
   <si>
-    <t>5_590</t>
+    <t>2_590</t>
   </si>
   <si>
     <t>1024010_1000</t>
   </si>
   <si>
-    <t>4_100</t>
+    <t>11_100</t>
   </si>
   <si>
     <t>1024010_1100</t>
   </si>
   <si>
-    <t>4_110</t>
+    <t>11_110</t>
   </si>
   <si>
     <t>1024010_1200</t>
   </si>
   <si>
-    <t>4_120</t>
+    <t>11_120</t>
   </si>
   <si>
     <t>1024010_1300</t>
   </si>
   <si>
-    <t>4_130</t>
+    <t>11_130</t>
   </si>
   <si>
     <t>1024010_1400</t>
   </si>
   <si>
-    <t>4_140</t>
+    <t>11_140</t>
   </si>
   <si>
     <t>1024010_1500</t>
   </si>
   <si>
-    <t>4_150</t>
+    <t>11_150</t>
   </si>
   <si>
     <t>1024010_1600</t>
   </si>
   <si>
-    <t>4_160</t>
+    <t>11_160</t>
   </si>
   <si>
     <t>1024010_1700</t>
   </si>
   <si>
-    <t>4_170</t>
+    <t>11_170</t>
   </si>
   <si>
     <t>1024010_1800</t>
   </si>
   <si>
-    <t>4_180</t>
+    <t>11_180</t>
   </si>
   <si>
     <t>1024010_1900</t>
   </si>
   <si>
-    <t>4_190</t>
+    <t>11_190</t>
   </si>
   <si>
     <t>1024010_5000</t>
   </si>
   <si>
-    <t>4_200</t>
+    <t>11_200</t>
   </si>
   <si>
     <t>1024010_5100</t>
   </si>
   <si>
-    <t>4_210</t>
+    <t>11_210</t>
   </si>
   <si>
     <t>1024010_5200</t>
   </si>
   <si>
-    <t>4_220</t>
+    <t>11_220</t>
   </si>
   <si>
     <t>1024010_5300</t>
   </si>
   <si>
-    <t>4_230</t>
+    <t>11_230</t>
   </si>
   <si>
     <t>1024010_5400</t>
   </si>
   <si>
-    <t>4_240</t>
+    <t>11_240</t>
   </si>
   <si>
     <t>1024010_5500</t>
   </si>
   <si>
-    <t>4_250</t>
+    <t>11_250</t>
   </si>
   <si>
     <t>1024010_5600</t>
   </si>
   <si>
-    <t>4_260</t>
+    <t>11_260</t>
   </si>
   <si>
     <t>1024010_5700</t>
   </si>
   <si>
-    <t>4_270</t>
+    <t>11_270</t>
   </si>
   <si>
     <t>1024010_5800</t>
   </si>
   <si>
-    <t>4_280</t>
+    <t>11_280</t>
   </si>
   <si>
     <t>1024010_5900</t>
   </si>
   <si>
-    <t>4_290</t>
+    <t>11_290</t>
   </si>
   <si>
     <t>1024010_10000</t>
   </si>
   <si>
-    <t>4_300</t>
+    <t>11_300</t>
   </si>
   <si>
     <t>1024010_10100</t>
   </si>
   <si>
-    <t>4_310</t>
+    <t>11_310</t>
   </si>
   <si>
     <t>1024010_10200</t>
   </si>
   <si>
-    <t>4_320</t>
+    <t>11_320</t>
   </si>
   <si>
     <t>1024010_10300</t>
   </si>
   <si>
-    <t>4_330</t>
+    <t>11_330</t>
   </si>
   <si>
     <t>1024010_10400</t>
   </si>
   <si>
-    <t>4_340</t>
+    <t>11_340</t>
   </si>
   <si>
     <t>1024010_10500</t>
   </si>
   <si>
-    <t>4_350</t>
+    <t>11_350</t>
   </si>
   <si>
     <t>1024010_10600</t>
   </si>
   <si>
-    <t>4_360</t>
+    <t>11_360</t>
   </si>
   <si>
     <t>1024010_10700</t>
   </si>
   <si>
-    <t>4_370</t>
+    <t>11_370</t>
   </si>
   <si>
     <t>1024010_10800</t>
   </si>
   <si>
-    <t>4_380</t>
+    <t>11_380</t>
   </si>
   <si>
     <t>1024010_10900</t>
   </si>
   <si>
-    <t>4_390</t>
+    <t>11_390</t>
   </si>
   <si>
     <t>1024010_15000</t>
   </si>
   <si>
-    <t>4_400</t>
+    <t>11_400</t>
   </si>
   <si>
     <t>1024010_15100</t>
   </si>
   <si>
-    <t>4_410</t>
+    <t>11_410</t>
   </si>
   <si>
     <t>1024010_15200</t>
   </si>
   <si>
-    <t>4_420</t>
+    <t>11_420</t>
   </si>
   <si>
     <t>1024010_15300</t>
   </si>
   <si>
-    <t>4_430</t>
+    <t>11_430</t>
   </si>
   <si>
     <t>1024010_15400</t>
   </si>
   <si>
-    <t>4_440</t>
+    <t>11_440</t>
   </si>
   <si>
     <t>1024010_15500</t>
   </si>
   <si>
-    <t>4_450</t>
+    <t>11_450</t>
   </si>
   <si>
     <t>1024010_15600</t>
   </si>
   <si>
-    <t>4_460</t>
+    <t>11_460</t>
   </si>
   <si>
     <t>1024010_15700</t>
   </si>
   <si>
-    <t>4_470</t>
+    <t>11_470</t>
   </si>
   <si>
     <t>1024010_15800</t>
   </si>
   <si>
-    <t>4_480</t>
+    <t>11_480</t>
   </si>
   <si>
     <t>1024010_15900</t>
   </si>
   <si>
-    <t>4_490</t>
+    <t>11_490</t>
   </si>
   <si>
     <t>1024010_20000</t>
   </si>
   <si>
-    <t>4_500</t>
+    <t>11_500</t>
   </si>
   <si>
     <t>1024010_20100</t>
   </si>
   <si>
-    <t>4_510</t>
+    <t>11_510</t>
   </si>
   <si>
     <t>1024010_20200</t>
   </si>
   <si>
-    <t>4_520</t>
+    <t>11_520</t>
   </si>
   <si>
     <t>1024010_20300</t>
   </si>
   <si>
-    <t>4_530</t>
+    <t>11_530</t>
   </si>
   <si>
     <t>1024010_20400</t>
   </si>
   <si>
-    <t>4_540</t>
+    <t>11_540</t>
   </si>
   <si>
     <t>1024010_20500</t>
   </si>
   <si>
-    <t>4_550</t>
+    <t>11_550</t>
   </si>
   <si>
     <t>1024010_20600</t>
   </si>
   <si>
-    <t>4_560</t>
+    <t>11_560</t>
   </si>
   <si>
     <t>1024010_20700</t>
   </si>
   <si>
-    <t>4_570</t>
+    <t>11_570</t>
   </si>
   <si>
     <t>1024010_20800</t>
   </si>
   <si>
-    <t>4_580</t>
+    <t>11_580</t>
   </si>
   <si>
     <t>1024010_20900</t>
   </si>
   <si>
-    <t>4_590</t>
+    <t>11_590</t>
   </si>
 </sst>
 </file>
@@ -1110,18 +1114,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1131,12 +1135,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1474,7 +1472,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1498,16 +1496,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1516,89 +1514,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1616,9 +1614,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4927,7 +4922,7 @@
       <c r="D155" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E155" s="6" t="s">
+      <c r="E155" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4945,7 +4940,7 @@
       <c r="D156" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E156" s="6" t="s">
+      <c r="E156" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4963,7 +4958,7 @@
       <c r="D157" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E157" s="6" t="s">
+      <c r="E157" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4981,7 +4976,7 @@
       <c r="D158" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E158" s="6" t="s">
+      <c r="E158" s="4" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4999,7 +4994,7 @@
       <c r="D159" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E159" s="6" t="s">
+      <c r="E159" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5017,7 +5012,7 @@
       <c r="D160" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E160" s="6" t="s">
+      <c r="E160" s="4" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5035,7 +5030,7 @@
       <c r="D161" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E161" s="6" t="s">
+      <c r="E161" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5053,7 +5048,7 @@
       <c r="D162" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E162" s="6" t="s">
+      <c r="E162" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5071,7 +5066,7 @@
       <c r="D163" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E163" s="6" t="s">
+      <c r="E163" s="4" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5089,7 +5084,7 @@
       <c r="D164" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E164" s="6" t="s">
+      <c r="E164" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5287,7 +5282,7 @@
       <c r="D175" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E175" s="6" t="s">
+      <c r="E175" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5305,7 +5300,7 @@
       <c r="D176" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E176" s="6" t="s">
+      <c r="E176" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5323,7 +5318,7 @@
       <c r="D177" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E177" s="6" t="s">
+      <c r="E177" s="4" t="s">
         <v>52</v>
       </c>
     </row>
@@ -5341,7 +5336,7 @@
       <c r="D178" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E178" s="6" t="s">
+      <c r="E178" s="4" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5359,7 +5354,7 @@
       <c r="D179" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E179" s="6" t="s">
+      <c r="E179" s="4" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5377,7 +5372,7 @@
       <c r="D180" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E180" s="6" t="s">
+      <c r="E180" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5395,7 +5390,7 @@
       <c r="D181" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E181" s="6" t="s">
+      <c r="E181" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -5413,7 +5408,7 @@
       <c r="D182" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E182" s="6" t="s">
+      <c r="E182" s="4" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5431,7 +5426,7 @@
       <c r="D183" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E183" s="6" t="s">
+      <c r="E183" s="4" t="s">
         <v>62</v>
       </c>
     </row>
@@ -5449,7 +5444,7 @@
       <c r="D184" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E184" s="6" t="s">
+      <c r="E184" s="4" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5647,7 +5642,7 @@
       <c r="D195" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E195" s="6" t="s">
+      <c r="E195" s="4" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5665,7 +5660,7 @@
       <c r="D196" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E196" s="6" t="s">
+      <c r="E196" s="4" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5683,7 +5678,7 @@
       <c r="D197" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E197" s="6" t="s">
+      <c r="E197" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5701,7 +5696,7 @@
       <c r="D198" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E198" s="6" t="s">
+      <c r="E198" s="4" t="s">
         <v>84</v>
       </c>
     </row>
@@ -5719,7 +5714,7 @@
       <c r="D199" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E199" s="6" t="s">
+      <c r="E199" s="4" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5737,7 +5732,7 @@
       <c r="D200" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E200" s="6" t="s">
+      <c r="E200" s="4" t="s">
         <v>87</v>
       </c>
     </row>
@@ -5755,7 +5750,7 @@
       <c r="D201" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E201" s="6" t="s">
+      <c r="E201" s="4" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5773,7 +5768,7 @@
       <c r="D202" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E202" s="6" t="s">
+      <c r="E202" s="4" t="s">
         <v>90</v>
       </c>
     </row>
@@ -5791,7 +5786,7 @@
       <c r="D203" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E203" s="6" t="s">
+      <c r="E203" s="4" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5809,7 +5804,7 @@
       <c r="D204" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E204" s="6" t="s">
+      <c r="E204" s="4" t="s">
         <v>93</v>
       </c>
     </row>
@@ -6007,7 +6002,7 @@
       <c r="D215" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E215" s="6" t="s">
+      <c r="E215" s="4" t="s">
         <v>115</v>
       </c>
     </row>
@@ -6025,7 +6020,7 @@
       <c r="D216" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E216" s="6" t="s">
+      <c r="E216" s="4" t="s">
         <v>117</v>
       </c>
     </row>
@@ -6043,7 +6038,7 @@
       <c r="D217" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E217" s="6" t="s">
+      <c r="E217" s="4" t="s">
         <v>119</v>
       </c>
     </row>
@@ -6061,7 +6056,7 @@
       <c r="D218" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E218" s="6" t="s">
+      <c r="E218" s="4" t="s">
         <v>121</v>
       </c>
     </row>
@@ -6079,7 +6074,7 @@
       <c r="D219" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E219" s="6" t="s">
+      <c r="E219" s="4" t="s">
         <v>123</v>
       </c>
     </row>
@@ -6097,7 +6092,7 @@
       <c r="D220" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E220" s="6" t="s">
+      <c r="E220" s="4" t="s">
         <v>125</v>
       </c>
     </row>
@@ -6115,7 +6110,7 @@
       <c r="D221" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E221" s="6" t="s">
+      <c r="E221" s="4" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6133,7 +6128,7 @@
       <c r="D222" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E222" s="6" t="s">
+      <c r="E222" s="4" t="s">
         <v>129</v>
       </c>
     </row>
@@ -6151,7 +6146,7 @@
       <c r="D223" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E223" s="6" t="s">
+      <c r="E223" s="4" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6169,7 +6164,7 @@
       <c r="D224" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E224" s="6" t="s">
+      <c r="E224" s="4" t="s">
         <v>133</v>
       </c>
     </row>
@@ -6367,7 +6362,7 @@
       <c r="D235" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E235" s="6" t="s">
+      <c r="E235" s="4" t="s">
         <v>155</v>
       </c>
     </row>
@@ -6385,7 +6380,7 @@
       <c r="D236" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E236" s="6" t="s">
+      <c r="E236" s="4" t="s">
         <v>157</v>
       </c>
     </row>
@@ -6403,7 +6398,7 @@
       <c r="D237" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E237" s="6" t="s">
+      <c r="E237" s="4" t="s">
         <v>159</v>
       </c>
     </row>
@@ -6421,7 +6416,7 @@
       <c r="D238" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E238" s="6" t="s">
+      <c r="E238" s="4" t="s">
         <v>161</v>
       </c>
     </row>
@@ -6439,7 +6434,7 @@
       <c r="D239" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E239" s="6" t="s">
+      <c r="E239" s="4" t="s">
         <v>163</v>
       </c>
     </row>
@@ -6457,7 +6452,7 @@
       <c r="D240" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E240" s="6" t="s">
+      <c r="E240" s="4" t="s">
         <v>165</v>
       </c>
     </row>
@@ -6475,7 +6470,7 @@
       <c r="D241" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E241" s="6" t="s">
+      <c r="E241" s="4" t="s">
         <v>167</v>
       </c>
     </row>
@@ -6493,7 +6488,7 @@
       <c r="D242" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E242" s="6" t="s">
+      <c r="E242" s="4" t="s">
         <v>169</v>
       </c>
     </row>
@@ -6511,7 +6506,7 @@
       <c r="D243" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E243" s="6" t="s">
+      <c r="E243" s="4" t="s">
         <v>171</v>
       </c>
     </row>
@@ -6529,7 +6524,7 @@
       <c r="D244" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E244" s="6" t="s">
+      <c r="E244" s="4" t="s">
         <v>173</v>
       </c>
     </row>
@@ -6727,7 +6722,7 @@
       <c r="D255" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="E255" s="6" t="s">
+      <c r="E255" s="4" t="s">
         <v>195</v>
       </c>
     </row>
@@ -6745,7 +6740,7 @@
       <c r="D256" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E256" s="6" t="s">
+      <c r="E256" s="4" t="s">
         <v>197</v>
       </c>
     </row>
@@ -6763,7 +6758,7 @@
       <c r="D257" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E257" s="6" t="s">
+      <c r="E257" s="4" t="s">
         <v>199</v>
       </c>
     </row>
@@ -6781,7 +6776,7 @@
       <c r="D258" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E258" s="6" t="s">
+      <c r="E258" s="4" t="s">
         <v>201</v>
       </c>
     </row>
@@ -6799,7 +6794,7 @@
       <c r="D259" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E259" s="6" t="s">
+      <c r="E259" s="4" t="s">
         <v>203</v>
       </c>
     </row>
@@ -6817,7 +6812,7 @@
       <c r="D260" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E260" s="6" t="s">
+      <c r="E260" s="4" t="s">
         <v>205</v>
       </c>
     </row>
@@ -6835,7 +6830,7 @@
       <c r="D261" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E261" s="6" t="s">
+      <c r="E261" s="4" t="s">
         <v>207</v>
       </c>
     </row>
@@ -6853,7 +6848,7 @@
       <c r="D262" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E262" s="6" t="s">
+      <c r="E262" s="4" t="s">
         <v>209</v>
       </c>
     </row>
@@ -6871,7 +6866,7 @@
       <c r="D263" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E263" s="6" t="s">
+      <c r="E263" s="4" t="s">
         <v>211</v>
       </c>
     </row>
@@ -6889,7 +6884,7 @@
       <c r="D264" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E264" s="6" t="s">
+      <c r="E264" s="4" t="s">
         <v>213</v>
       </c>
     </row>
@@ -7087,7 +7082,7 @@
       <c r="D275" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="E275" s="6" t="s">
+      <c r="E275" s="4" t="s">
         <v>235</v>
       </c>
     </row>
@@ -7105,7 +7100,7 @@
       <c r="D276" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E276" s="6" t="s">
+      <c r="E276" s="4" t="s">
         <v>237</v>
       </c>
     </row>
@@ -7123,7 +7118,7 @@
       <c r="D277" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E277" s="6" t="s">
+      <c r="E277" s="4" t="s">
         <v>239</v>
       </c>
     </row>
@@ -7141,7 +7136,7 @@
       <c r="D278" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E278" s="6" t="s">
+      <c r="E278" s="4" t="s">
         <v>241</v>
       </c>
     </row>
@@ -7159,7 +7154,7 @@
       <c r="D279" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="E279" s="6" t="s">
+      <c r="E279" s="4" t="s">
         <v>243</v>
       </c>
     </row>
@@ -7177,7 +7172,7 @@
       <c r="D280" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="E280" s="6" t="s">
+      <c r="E280" s="4" t="s">
         <v>245</v>
       </c>
     </row>
@@ -7195,7 +7190,7 @@
       <c r="D281" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E281" s="6" t="s">
+      <c r="E281" s="4" t="s">
         <v>247</v>
       </c>
     </row>
@@ -7213,7 +7208,7 @@
       <c r="D282" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="E282" s="6" t="s">
+      <c r="E282" s="4" t="s">
         <v>249</v>
       </c>
     </row>
@@ -7231,7 +7226,7 @@
       <c r="D283" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="E283" s="6" t="s">
+      <c r="E283" s="4" t="s">
         <v>251</v>
       </c>
     </row>
@@ -7249,7 +7244,7 @@
       <c r="D284" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E284" s="6" t="s">
+      <c r="E284" s="4" t="s">
         <v>253</v>
       </c>
     </row>
@@ -7447,7 +7442,7 @@
       <c r="D295" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E295" s="6" t="s">
+      <c r="E295" s="4" t="s">
         <v>275</v>
       </c>
     </row>
@@ -7465,7 +7460,7 @@
       <c r="D296" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="E296" s="6" t="s">
+      <c r="E296" s="4" t="s">
         <v>277</v>
       </c>
     </row>
@@ -7483,7 +7478,7 @@
       <c r="D297" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E297" s="6" t="s">
+      <c r="E297" s="4" t="s">
         <v>279</v>
       </c>
     </row>
@@ -7501,7 +7496,7 @@
       <c r="D298" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E298" s="6" t="s">
+      <c r="E298" s="4" t="s">
         <v>281</v>
       </c>
     </row>
@@ -7519,7 +7514,7 @@
       <c r="D299" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E299" s="6" t="s">
+      <c r="E299" s="4" t="s">
         <v>283</v>
       </c>
     </row>
@@ -7537,7 +7532,7 @@
       <c r="D300" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E300" s="6" t="s">
+      <c r="E300" s="4" t="s">
         <v>285</v>
       </c>
     </row>
@@ -7555,7 +7550,7 @@
       <c r="D301" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="E301" s="6" t="s">
+      <c r="E301" s="4" t="s">
         <v>287</v>
       </c>
     </row>
@@ -7573,7 +7568,7 @@
       <c r="D302" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="E302" s="6" t="s">
+      <c r="E302" s="4" t="s">
         <v>289</v>
       </c>
     </row>
@@ -7591,7 +7586,7 @@
       <c r="D303" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="E303" s="6" t="s">
+      <c r="E303" s="4" t="s">
         <v>291</v>
       </c>
     </row>
@@ -7609,7 +7604,7 @@
       <c r="D304" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="E304" s="6" t="s">
+      <c r="E304" s="4" t="s">
         <v>293</v>
       </c>
     </row>
@@ -7618,4 +7613,235 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="E16:K25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="16" spans="5:11">
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>500</v>
+      </c>
+      <c r="H16" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,$I$101,F16)</f>
+        <v>500</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" ref="I16:I25" si="0">_xlfn.TEXTJOIN("_",TRUE,$I$103,F16)</f>
+        <v>500</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" ref="J16:J25" si="1">_xlfn.TEXTJOIN("_",TRUE,$I$104,F16)</f>
+        <v>500</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" ref="K16:K25" si="2">_xlfn.TEXTJOIN("|",TRUE,H16:J16)</f>
+        <v>500|500|500</v>
+      </c>
+    </row>
+    <row r="17" spans="5:11">
+      <c r="F17">
+        <v>510</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" ref="H16:H25" si="3">_xlfn.TEXTJOIN("_",TRUE,$I$101,F17)</f>
+        <v>510</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="0"/>
+        <v>510</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="1"/>
+        <v>510</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="2"/>
+        <v>510|510|510</v>
+      </c>
+    </row>
+    <row r="18" spans="5:11">
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18">
+        <v>520</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="3"/>
+        <v>520</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="1"/>
+        <v>520</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="2"/>
+        <v>520|520|520</v>
+      </c>
+    </row>
+    <row r="19" spans="5:11">
+      <c r="E19">
+        <v>6</v>
+      </c>
+      <c r="F19">
+        <v>530</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="3"/>
+        <v>530</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="0"/>
+        <v>530</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="1"/>
+        <v>530</v>
+      </c>
+      <c r="K19" t="str">
+        <f t="shared" si="2"/>
+        <v>530|530|530</v>
+      </c>
+    </row>
+    <row r="20" spans="5:11">
+      <c r="F20">
+        <v>540</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="0"/>
+        <v>540</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="1"/>
+        <v>540</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="2"/>
+        <v>540|540|540</v>
+      </c>
+    </row>
+    <row r="21" spans="5:11">
+      <c r="F21">
+        <v>550</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="3"/>
+        <v>550</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="0"/>
+        <v>550</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="1"/>
+        <v>550</v>
+      </c>
+      <c r="K21" t="str">
+        <f t="shared" si="2"/>
+        <v>550|550|550</v>
+      </c>
+    </row>
+    <row r="22" spans="5:11">
+      <c r="F22">
+        <v>560</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="3"/>
+        <v>560</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="0"/>
+        <v>560</v>
+      </c>
+      <c r="J22" t="str">
+        <f t="shared" si="1"/>
+        <v>560</v>
+      </c>
+      <c r="K22" t="str">
+        <f t="shared" si="2"/>
+        <v>560|560|560</v>
+      </c>
+    </row>
+    <row r="23" spans="5:11">
+      <c r="F23">
+        <v>570</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="3"/>
+        <v>570</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J23" t="str">
+        <f t="shared" si="1"/>
+        <v>570</v>
+      </c>
+      <c r="K23" t="str">
+        <f t="shared" si="2"/>
+        <v>570|570|570</v>
+      </c>
+    </row>
+    <row r="24" spans="5:11">
+      <c r="F24">
+        <v>580</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="3"/>
+        <v>580</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="0"/>
+        <v>580</v>
+      </c>
+      <c r="J24" t="str">
+        <f t="shared" si="1"/>
+        <v>580</v>
+      </c>
+      <c r="K24" t="str">
+        <f t="shared" si="2"/>
+        <v>580|580|580</v>
+      </c>
+    </row>
+    <row r="25" spans="5:11">
+      <c r="F25">
+        <v>590</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="3"/>
+        <v>590</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="0"/>
+        <v>590</v>
+      </c>
+      <c r="J25" t="str">
+        <f t="shared" si="1"/>
+        <v>590</v>
+      </c>
+      <c r="K25" t="str">
+        <f t="shared" si="2"/>
+        <v>590|590|590</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>